--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel M\Desktop\Modulo02_JavaScript\00000_Correcciones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34FDDEC-18C0-4184-8C87-7584DC0DFFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$3:$K$67</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="87">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -293,7 +294,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -375,12 +376,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -660,7 +661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:K67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -677,14 +678,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
@@ -697,23 +698,23 @@
       <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -975,7 +976,7 @@
       <c r="C18" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E18" t="s">
@@ -1004,7 +1005,7 @@
       <c r="C19" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E19" t="s">
@@ -1086,7 +1087,7 @@
       <c r="B24">
         <v>21</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>28</v>
       </c>
       <c r="E24" t="s">
@@ -1109,7 +1110,7 @@
       <c r="B25">
         <v>22</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E25" t="s">
@@ -1205,12 +1206,21 @@
       <c r="F30">
         <v>8</v>
       </c>
+      <c r="H30">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>7</v>
+      </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>28</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E31" t="s">
@@ -1262,7 +1272,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="7" t="s">
         <v>38</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -1314,6 +1324,15 @@
       <c r="F36">
         <v>8</v>
       </c>
+      <c r="H36">
+        <v>18</v>
+      </c>
+      <c r="I36" t="s">
+        <v>2</v>
+      </c>
+      <c r="J36">
+        <v>5</v>
+      </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37">
@@ -1426,6 +1445,15 @@
       <c r="F44">
         <v>8</v>
       </c>
+      <c r="H44">
+        <v>19</v>
+      </c>
+      <c r="I44" t="s">
+        <v>2</v>
+      </c>
+      <c r="J44">
+        <v>10</v>
+      </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45">
@@ -1454,6 +1482,15 @@
       <c r="F46">
         <v>8</v>
       </c>
+      <c r="H46">
+        <v>20</v>
+      </c>
+      <c r="I46" t="s">
+        <v>2</v>
+      </c>
+      <c r="J46">
+        <v>7</v>
+      </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="3">
@@ -1506,7 +1543,7 @@
       <c r="B49">
         <v>46</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="7" t="s">
         <v>56</v>
       </c>
       <c r="E49" t="s">
@@ -1575,6 +1612,15 @@
       <c r="F52">
         <v>8</v>
       </c>
+      <c r="H52">
+        <v>17</v>
+      </c>
+      <c r="I52" t="s">
+        <v>2</v>
+      </c>
+      <c r="J52">
+        <v>7</v>
+      </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53">
@@ -1648,7 +1694,7 @@
       <c r="B57">
         <v>54</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="7" t="s">
         <v>64</v>
       </c>
       <c r="E57" t="s">
@@ -1697,7 +1743,7 @@
       <c r="B59">
         <v>56</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="7" t="s">
         <v>66</v>
       </c>
       <c r="E59" t="s">
@@ -1829,7 +1875,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:K67"/>
+  <autoFilter ref="B3:K67" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34FDDEC-18C0-4184-8C87-7584DC0DFFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C300E46C-4C3D-4D16-9B00-4EA8B6F9A787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="90">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -289,13 +289,22 @@
   </si>
   <si>
     <t>Excelente Colega</t>
+  </si>
+  <si>
+    <t>Utilizó 100% IA</t>
+  </si>
+  <si>
+    <t>Faltan los documentos HTML, no se pueden ejecutar</t>
+  </si>
+  <si>
+    <t>Idéntica presentación a la de otro alumno</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,8 +320,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -355,6 +372,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -368,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -382,6 +405,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,15 +689,15 @@
   <dimension ref="B2:K67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="8.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="6" max="6" width="3.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="54.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="50.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -719,126 +743,191 @@
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4">
+      <c r="B4" s="3">
+        <v>31</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>8</v>
+      <c r="I4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>7</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>3</v>
+        <v>54</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="E5" t="s">
         <v>2</v>
       </c>
       <c r="F5">
         <v>8</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6">
+        <v>56</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="H6">
         <v>3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="I6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>46</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="H7">
         <v>4</v>
       </c>
-      <c r="E6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="I7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>28</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="2">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="2">
-        <v>2</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="2"/>
+      <c r="I8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>8</v>
+      </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9">
+        <v>22</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="H9">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>8</v>
+      <c r="I9" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="H10">
         <v>7</v>
       </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="I10" t="s">
         <v>6</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
+        <v>81</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="E11" t="s">
         <v>2</v>
@@ -847,7 +936,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I11" t="s">
         <v>6</v>
@@ -856,38 +945,47 @@
         <v>2</v>
       </c>
       <c r="K11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12">
+        <v>21</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="H12">
         <v>9</v>
       </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12">
-        <v>8</v>
+      <c r="I12" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>8</v>
+      </c>
+      <c r="H13">
         <v>10</v>
-      </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F13">
-        <v>8</v>
-      </c>
-      <c r="H13">
-        <v>14</v>
       </c>
       <c r="I13" t="s">
         <v>2</v>
@@ -895,319 +993,423 @@
       <c r="J13">
         <v>7</v>
       </c>
-      <c r="K13" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>8</v>
+      </c>
+      <c r="H14">
         <v>11</v>
       </c>
-      <c r="D14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s">
-        <v>2</v>
-      </c>
-      <c r="F14">
-        <v>8</v>
+      <c r="I14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>7</v>
+      </c>
+      <c r="K14" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+      <c r="H15">
+        <v>12</v>
+      </c>
+      <c r="I15" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="2">
-        <v>2</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="2"/>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="H16">
         <v>13</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="2">
-        <v>2</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="2"/>
+      <c r="I16" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>7</v>
+      </c>
+      <c r="K16" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
         <v>14</v>
       </c>
-      <c r="D17" t="s">
-        <v>21</v>
-      </c>
       <c r="E17" t="s">
         <v>2</v>
       </c>
       <c r="F17">
         <v>8</v>
+      </c>
+      <c r="H17">
+        <v>14</v>
+      </c>
+      <c r="I17" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>7</v>
+      </c>
+      <c r="K17" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18">
+        <v>45</v>
+      </c>
+      <c r="D18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="H18">
         <v>15</v>
       </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" t="s">
-        <v>2</v>
-      </c>
-      <c r="F18">
-        <v>8</v>
-      </c>
-      <c r="H18">
-        <v>8</v>
-      </c>
       <c r="I18" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K18" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>8</v>
+      </c>
+      <c r="H19">
         <v>16</v>
       </c>
-      <c r="C19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" t="s">
-        <v>2</v>
-      </c>
-      <c r="F19">
-        <v>8</v>
-      </c>
-      <c r="H19">
+      <c r="I19" t="s">
+        <v>2</v>
+      </c>
+      <c r="J19">
         <v>7</v>
-      </c>
-      <c r="I19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J19">
-        <v>2</v>
-      </c>
-      <c r="K19" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>8</v>
+      </c>
+      <c r="H20">
         <v>17</v>
       </c>
-      <c r="D20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F20">
-        <v>8</v>
+      <c r="I20" t="s">
+        <v>2</v>
+      </c>
+      <c r="J20">
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>8</v>
+      </c>
+      <c r="H21">
         <v>18</v>
       </c>
-      <c r="D21" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21">
-        <v>8</v>
+      <c r="I21" t="s">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22">
+        <v>41</v>
+      </c>
+      <c r="D22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>8</v>
+      </c>
+      <c r="H22">
         <v>19</v>
       </c>
-      <c r="D22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22">
-        <v>8</v>
+      <c r="I22" t="s">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23">
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>8</v>
+      </c>
+      <c r="H23">
         <v>20</v>
       </c>
-      <c r="D23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F23">
-        <v>8</v>
+      <c r="I23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <v>7</v>
+      </c>
+      <c r="H24">
         <v>21</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" t="s">
-        <v>2</v>
-      </c>
-      <c r="F24">
-        <v>8</v>
-      </c>
-      <c r="H24">
-        <v>9</v>
-      </c>
       <c r="I24" t="s">
         <v>2</v>
       </c>
       <c r="J24">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="K24" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>8</v>
+      </c>
+      <c r="H25">
         <v>22</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" t="s">
-        <v>2</v>
-      </c>
-      <c r="F25">
-        <v>8</v>
-      </c>
-      <c r="H25">
+      <c r="I25" t="s">
         <v>6</v>
       </c>
-      <c r="I25" t="s">
-        <v>2</v>
-      </c>
       <c r="J25">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K25" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="H26">
         <v>23</v>
       </c>
-      <c r="D26" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" t="s">
-        <v>2</v>
-      </c>
-      <c r="F26">
+      <c r="I26" t="s">
+        <v>2</v>
+      </c>
+      <c r="J26">
         <v>8</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="2">
+        <v>2</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="2">
         <v>24</v>
       </c>
-      <c r="D27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F27">
-        <v>8</v>
+      <c r="I27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28">
+        <v>34</v>
+      </c>
+      <c r="D28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>8</v>
+      </c>
+      <c r="H28">
         <v>25</v>
       </c>
-      <c r="D28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" t="s">
-        <v>2</v>
-      </c>
-      <c r="F28">
-        <v>8</v>
+      <c r="I28" t="s">
+        <v>2</v>
+      </c>
+      <c r="J28">
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="2">
+      <c r="B29">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>8</v>
+      </c>
+      <c r="H29">
         <v>26</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" s="2">
-        <v>2</v>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
+      <c r="I29" t="s">
+        <v>2</v>
+      </c>
+      <c r="J29">
+        <v>8</v>
+      </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
+      </c>
+      <c r="H30">
         <v>27</v>
-      </c>
-      <c r="D30" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30">
-        <v>8</v>
-      </c>
-      <c r="H30">
-        <v>16</v>
       </c>
       <c r="I30" t="s">
         <v>2</v>
@@ -1218,33 +1420,24 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31">
-        <v>28</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
+      </c>
+      <c r="D31" t="s">
+        <v>36</v>
       </c>
       <c r="E31" t="s">
         <v>2</v>
       </c>
       <c r="F31">
-        <v>8</v>
-      </c>
-      <c r="H31">
-        <v>5</v>
-      </c>
-      <c r="I31" t="s">
-        <v>2</v>
-      </c>
-      <c r="J31">
         <v>8</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E32" t="s">
         <v>2</v>
@@ -1255,10 +1448,10 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E33" t="s">
         <v>2</v>
@@ -1268,78 +1461,67 @@
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B34" s="3">
-        <v>31</v>
-      </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="3" t="s">
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="D34" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="2">
+        <v>4</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F34" s="3">
-        <v>2</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H34" s="3">
-        <v>1</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J34">
+      <c r="F35" s="2">
+        <v>2</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" s="2">
+        <v>5</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K34" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B35">
-        <v>32</v>
-      </c>
-      <c r="D35" t="s">
-        <v>40</v>
-      </c>
-      <c r="E35" t="s">
-        <v>2</v>
-      </c>
-      <c r="F35">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36">
-        <v>33</v>
-      </c>
-      <c r="D36" t="s">
-        <v>41</v>
-      </c>
-      <c r="E36" t="s">
-        <v>2</v>
-      </c>
-      <c r="F36">
-        <v>8</v>
-      </c>
-      <c r="H36">
-        <v>18</v>
-      </c>
-      <c r="I36" t="s">
-        <v>2</v>
-      </c>
-      <c r="J36">
-        <v>5</v>
-      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" s="2">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H36" s="2"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="E37" t="s">
         <v>2</v>
@@ -1349,25 +1531,27 @@
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38">
-        <v>35</v>
-      </c>
-      <c r="D38" t="s">
-        <v>43</v>
-      </c>
-      <c r="E38" t="s">
-        <v>2</v>
-      </c>
-      <c r="F38">
-        <v>8</v>
-      </c>
+      <c r="B38" s="9">
+        <v>7</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="D39" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
         <v>2</v>
@@ -1378,10 +1562,10 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
         <v>2</v>
@@ -1392,24 +1576,42 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41">
-        <v>38</v>
-      </c>
-      <c r="D41" t="s">
-        <v>46</v>
-      </c>
-      <c r="E41" t="s">
-        <v>2</v>
-      </c>
-      <c r="F41">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" s="2">
+        <v>2</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="2">
+        <v>29</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="E42" t="s">
         <v>2</v>
@@ -1420,10 +1622,10 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E43" t="s">
         <v>2</v>
@@ -1434,33 +1636,24 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E44" t="s">
         <v>2</v>
       </c>
       <c r="F44">
         <v>8</v>
-      </c>
-      <c r="H44">
-        <v>19</v>
-      </c>
-      <c r="I44" t="s">
-        <v>2</v>
-      </c>
-      <c r="J44">
-        <v>10</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="E45" t="s">
         <v>2</v>
@@ -1471,312 +1664,245 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46">
+        <v>23</v>
+      </c>
+      <c r="D46" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2</v>
+      </c>
+      <c r="F46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B47">
+        <v>25</v>
+      </c>
+      <c r="D47" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2</v>
+      </c>
+      <c r="F47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="2">
+        <v>26</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F48" s="2">
+        <v>2</v>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <v>30</v>
+      </c>
+      <c r="D49" t="s">
+        <v>37</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2</v>
+      </c>
+      <c r="F49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>32</v>
+      </c>
+      <c r="D50" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50">
+        <v>8</v>
+      </c>
+      <c r="H50">
+        <v>28</v>
+      </c>
+      <c r="I50" t="s">
+        <v>2</v>
+      </c>
+      <c r="J50">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <v>35</v>
+      </c>
+      <c r="D51" t="s">
         <v>43</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E51" t="s">
+        <v>2</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>36</v>
+      </c>
+      <c r="D52" t="s">
+        <v>44</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>37</v>
+      </c>
+      <c r="D53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>40</v>
+      </c>
+      <c r="D54" t="s">
+        <v>48</v>
+      </c>
+      <c r="E54" t="s">
+        <v>2</v>
+      </c>
+      <c r="F54">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <v>42</v>
+      </c>
+      <c r="D55" t="s">
+        <v>50</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="3">
+        <v>44</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F56" s="3">
+        <v>2</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>48</v>
+      </c>
+      <c r="D57" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" t="s">
+        <v>2</v>
+      </c>
+      <c r="F57">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <v>50</v>
+      </c>
+      <c r="D58" t="s">
+        <v>60</v>
+      </c>
+      <c r="E58" t="s">
+        <v>2</v>
+      </c>
+      <c r="F58">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59">
         <v>51</v>
       </c>
-      <c r="E46" t="s">
-        <v>2</v>
-      </c>
-      <c r="F46">
-        <v>8</v>
-      </c>
-      <c r="H46">
-        <v>20</v>
-      </c>
-      <c r="I46" t="s">
-        <v>2</v>
-      </c>
-      <c r="J46">
+      <c r="D59" t="s">
+        <v>61</v>
+      </c>
+      <c r="E59" t="s">
+        <v>2</v>
+      </c>
+      <c r="F59">
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="3">
-        <v>44</v>
-      </c>
-      <c r="C47" s="3" t="s">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60">
         <v>53</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" s="3">
-        <v>2</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48">
-        <v>45</v>
-      </c>
-      <c r="D48" t="s">
-        <v>55</v>
-      </c>
-      <c r="E48" t="s">
-        <v>2</v>
-      </c>
-      <c r="F48">
-        <v>10</v>
-      </c>
-      <c r="H48">
-        <v>15</v>
-      </c>
-      <c r="I48" t="s">
-        <v>2</v>
-      </c>
-      <c r="J48">
-        <v>10</v>
-      </c>
-      <c r="K48" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B49">
-        <v>46</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E49" t="s">
-        <v>2</v>
-      </c>
-      <c r="F49">
-        <v>8</v>
-      </c>
-      <c r="H49">
-        <v>4</v>
-      </c>
-      <c r="I49" t="s">
-        <v>2</v>
-      </c>
-      <c r="J49">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B50">
-        <v>47</v>
-      </c>
-      <c r="D50" t="s">
-        <v>57</v>
-      </c>
-      <c r="E50" t="s">
-        <v>2</v>
-      </c>
-      <c r="F50">
-        <v>8</v>
-      </c>
-      <c r="H50">
-        <v>10</v>
-      </c>
-      <c r="I50" t="s">
-        <v>2</v>
-      </c>
-      <c r="J50">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B51">
-        <v>48</v>
-      </c>
-      <c r="D51" t="s">
-        <v>58</v>
-      </c>
-      <c r="E51" t="s">
-        <v>2</v>
-      </c>
-      <c r="F51">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B52">
-        <v>49</v>
-      </c>
-      <c r="D52" t="s">
-        <v>59</v>
-      </c>
-      <c r="E52" t="s">
-        <v>2</v>
-      </c>
-      <c r="F52">
-        <v>8</v>
-      </c>
-      <c r="H52">
-        <v>17</v>
-      </c>
-      <c r="I52" t="s">
-        <v>2</v>
-      </c>
-      <c r="J52">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B53">
-        <v>50</v>
-      </c>
-      <c r="D53" t="s">
-        <v>60</v>
-      </c>
-      <c r="E53" t="s">
-        <v>2</v>
-      </c>
-      <c r="F53">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B54">
-        <v>51</v>
-      </c>
-      <c r="D54" t="s">
-        <v>61</v>
-      </c>
-      <c r="E54" t="s">
-        <v>2</v>
-      </c>
-      <c r="F54">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B55">
-        <v>52</v>
-      </c>
-      <c r="D55" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55" t="s">
-        <v>2</v>
-      </c>
-      <c r="F55">
-        <v>9</v>
-      </c>
-      <c r="H55">
-        <v>13</v>
-      </c>
-      <c r="I55" t="s">
-        <v>2</v>
-      </c>
-      <c r="J55">
-        <v>7</v>
-      </c>
-      <c r="K55" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B56">
-        <v>53</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="D60" t="s">
         <v>63</v>
       </c>
-      <c r="E56" t="s">
-        <v>2</v>
-      </c>
-      <c r="F56">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B57">
-        <v>54</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E57" t="s">
-        <v>2</v>
-      </c>
-      <c r="F57">
-        <v>8</v>
-      </c>
-      <c r="H57">
-        <v>2</v>
-      </c>
-      <c r="I57" t="s">
-        <v>2</v>
-      </c>
-      <c r="J57">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B58">
-        <v>55</v>
-      </c>
-      <c r="D58" t="s">
-        <v>65</v>
-      </c>
-      <c r="E58" t="s">
-        <v>2</v>
-      </c>
-      <c r="F58">
-        <v>8</v>
-      </c>
-      <c r="H58">
-        <v>11</v>
-      </c>
-      <c r="I58" t="s">
-        <v>2</v>
-      </c>
-      <c r="J58">
-        <v>7</v>
-      </c>
-      <c r="K58" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B59">
-        <v>56</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E59" t="s">
-        <v>2</v>
-      </c>
-      <c r="F59">
-        <v>9</v>
-      </c>
-      <c r="H59">
-        <v>3</v>
-      </c>
-      <c r="I59" t="s">
-        <v>2</v>
-      </c>
-      <c r="J59">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B60">
-        <v>57</v>
-      </c>
-      <c r="D60" t="s">
-        <v>67</v>
-      </c>
       <c r="E60" t="s">
         <v>2</v>
       </c>
       <c r="F60">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H60">
+        <v>30</v>
+      </c>
+      <c r="I60" t="s">
+        <v>2</v>
+      </c>
+      <c r="J60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>58</v>
       </c>
@@ -1790,7 +1916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>59</v>
       </c>
@@ -1804,7 +1930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63">
         <v>60</v>
       </c>
@@ -1818,7 +1944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>61</v>
       </c>
@@ -1875,7 +2001,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:K67" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B3:K67" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:K67">
+      <sortCondition ref="H4:H67"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C300E46C-4C3D-4D16-9B00-4EA8B6F9A787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5915FD65-CF20-42BF-982C-EEB5124332F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="91">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>Idéntica presentación a la de otro alumno</t>
+  </si>
+  <si>
+    <t>el 40% se hizo con IA</t>
   </si>
 </sst>
 </file>
@@ -402,10 +405,8 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -702,14 +703,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
@@ -1420,52 +1421,88 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
         <v>2</v>
       </c>
       <c r="F31">
+        <v>8</v>
+      </c>
+      <c r="H31">
+        <v>28</v>
+      </c>
+      <c r="I31" t="s">
+        <v>2</v>
+      </c>
+      <c r="J31">
         <v>8</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="D32" t="s">
-        <v>0</v>
-      </c>
-      <c r="E32" t="s">
-        <v>2</v>
-      </c>
-      <c r="F32">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" s="2">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="2">
+        <v>29</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="D33" t="s">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="E33" t="s">
         <v>2</v>
       </c>
       <c r="F33">
         <v>8</v>
+      </c>
+      <c r="H33">
+        <v>30</v>
+      </c>
+      <c r="I33" t="s">
+        <v>2</v>
+      </c>
+      <c r="J33">
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E34" t="s">
         <v>2</v>
@@ -1473,55 +1510,71 @@
       <c r="F34">
         <v>8</v>
       </c>
+      <c r="H34">
+        <v>31</v>
+      </c>
+      <c r="I34" t="s">
+        <v>2</v>
+      </c>
+      <c r="J34">
+        <v>8</v>
+      </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B35" s="2">
-        <v>4</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="B35">
+        <v>50</v>
+      </c>
+      <c r="D35" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35">
+        <v>8</v>
+      </c>
+      <c r="H35">
+        <v>32</v>
+      </c>
+      <c r="I35" t="s">
+        <v>2</v>
+      </c>
+      <c r="J35">
         <v>9</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35" s="2" t="s">
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <v>20</v>
+      </c>
+      <c r="D36" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2</v>
+      </c>
+      <c r="F36">
+        <v>8</v>
+      </c>
+      <c r="H36">
+        <v>33</v>
+      </c>
+      <c r="I36" t="s">
+        <v>2</v>
+      </c>
+      <c r="J36">
         <v>6</v>
       </c>
-      <c r="F35" s="2">
-        <v>2</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="2">
-        <v>5</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" s="2">
-        <v>2</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H36" s="2"/>
+      <c r="K36" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E37" t="s">
         <v>2</v>
@@ -1529,117 +1582,160 @@
       <c r="F37">
         <v>8</v>
       </c>
+      <c r="H37">
+        <v>34</v>
+      </c>
+      <c r="I37" t="s">
+        <v>2</v>
+      </c>
+      <c r="J37">
+        <v>9</v>
+      </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="9">
-        <v>7</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
+      <c r="B38">
+        <v>29</v>
+      </c>
+      <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" t="s">
+        <v>2</v>
+      </c>
+      <c r="F38">
+        <v>8</v>
+      </c>
+      <c r="H38">
+        <v>35</v>
+      </c>
+      <c r="I38" t="s">
+        <v>2</v>
+      </c>
+      <c r="J38">
+        <v>8</v>
+      </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39">
+        <v>18</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="H39">
+        <v>36</v>
+      </c>
+      <c r="I39" t="s">
+        <v>2</v>
+      </c>
+      <c r="J39">
         <v>9</v>
-      </c>
-      <c r="D39" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" t="s">
-        <v>2</v>
-      </c>
-      <c r="F39">
-        <v>8</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="E40" t="s">
         <v>2</v>
       </c>
       <c r="F40">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H40">
+        <v>37</v>
+      </c>
+      <c r="I40" t="s">
+        <v>2</v>
+      </c>
+      <c r="J40">
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41">
-        <v>13</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" s="2">
-        <v>2</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H41" s="2">
-        <v>29</v>
-      </c>
-      <c r="I41" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" t="s">
+        <v>2</v>
+      </c>
+      <c r="F41">
+        <v>8</v>
+      </c>
+      <c r="H41">
+        <v>38</v>
+      </c>
+      <c r="I41" t="s">
         <v>2</v>
       </c>
       <c r="J41">
-        <v>2</v>
-      </c>
-      <c r="K41" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D42" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
         <v>2</v>
       </c>
       <c r="F42">
         <v>8</v>
+      </c>
+      <c r="H42">
+        <v>39</v>
+      </c>
+      <c r="I42" t="s">
+        <v>2</v>
+      </c>
+      <c r="J42">
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
         <v>2</v>
       </c>
       <c r="F43">
         <v>8</v>
+      </c>
+      <c r="H43">
+        <v>40</v>
+      </c>
+      <c r="I43" t="s">
+        <v>2</v>
+      </c>
+      <c r="J43">
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E44" t="s">
         <v>2</v>
@@ -1650,10 +1746,10 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="E45" t="s">
         <v>2</v>
@@ -1664,10 +1760,10 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E46" t="s">
         <v>2</v>
@@ -1677,28 +1773,35 @@
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47">
-        <v>25</v>
-      </c>
-      <c r="D47" t="s">
-        <v>32</v>
-      </c>
-      <c r="E47" t="s">
-        <v>2</v>
-      </c>
-      <c r="F47">
-        <v>8</v>
-      </c>
+      <c r="B47" s="2">
+        <v>4</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" s="2">
+        <v>2</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="2"/>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="2">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1706,203 +1809,194 @@
       <c r="F48" s="2">
         <v>2</v>
       </c>
-      <c r="G48" s="2"/>
+      <c r="G48" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49">
+        <v>6</v>
+      </c>
+      <c r="D49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2</v>
+      </c>
+      <c r="F49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="8">
+        <v>7</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <v>11</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>14</v>
+      </c>
+      <c r="D52" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>17</v>
+      </c>
+      <c r="D53" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>23</v>
+      </c>
+      <c r="D54" t="s">
         <v>30</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E54" t="s">
+        <v>2</v>
+      </c>
+      <c r="F54">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <v>25</v>
+      </c>
+      <c r="D55" t="s">
+        <v>32</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56" s="2">
+        <v>26</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F56" s="2">
+        <v>2</v>
+      </c>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>30</v>
+      </c>
+      <c r="D57" t="s">
         <v>37</v>
       </c>
-      <c r="E49" t="s">
-        <v>2</v>
-      </c>
-      <c r="F49">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50">
-        <v>32</v>
-      </c>
-      <c r="D50" t="s">
-        <v>40</v>
-      </c>
-      <c r="E50" t="s">
-        <v>2</v>
-      </c>
-      <c r="F50">
-        <v>8</v>
-      </c>
-      <c r="H50">
-        <v>28</v>
-      </c>
-      <c r="I50" t="s">
-        <v>2</v>
-      </c>
-      <c r="J50">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51">
+      <c r="E57" t="s">
+        <v>2</v>
+      </c>
+      <c r="F57">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B58">
         <v>35</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D58" t="s">
         <v>43</v>
       </c>
-      <c r="E51" t="s">
-        <v>2</v>
-      </c>
-      <c r="F51">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B52">
-        <v>36</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="E58" t="s">
+        <v>2</v>
+      </c>
+      <c r="F58">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B59" s="3">
         <v>44</v>
       </c>
-      <c r="E52" t="s">
-        <v>2</v>
-      </c>
-      <c r="F52">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53">
-        <v>37</v>
-      </c>
-      <c r="D53" t="s">
-        <v>45</v>
-      </c>
-      <c r="E53" t="s">
-        <v>2</v>
-      </c>
-      <c r="F53">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54">
-        <v>40</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C59" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B60">
         <v>48</v>
       </c>
-      <c r="E54" t="s">
-        <v>2</v>
-      </c>
-      <c r="F54">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B55">
-        <v>42</v>
-      </c>
-      <c r="D55" t="s">
-        <v>50</v>
-      </c>
-      <c r="E55" t="s">
-        <v>2</v>
-      </c>
-      <c r="F55">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B56" s="3">
-        <v>44</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" s="3">
-        <v>2</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H56" s="3"/>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57">
-        <v>48</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="D60" t="s">
         <v>58</v>
       </c>
-      <c r="E57" t="s">
-        <v>2</v>
-      </c>
-      <c r="F57">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58">
-        <v>50</v>
-      </c>
-      <c r="D58" t="s">
-        <v>60</v>
-      </c>
-      <c r="E58" t="s">
-        <v>2</v>
-      </c>
-      <c r="F58">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B59">
-        <v>51</v>
-      </c>
-      <c r="D59" t="s">
-        <v>61</v>
-      </c>
-      <c r="E59" t="s">
-        <v>2</v>
-      </c>
-      <c r="F59">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60">
-        <v>53</v>
-      </c>
-      <c r="D60" t="s">
-        <v>63</v>
-      </c>
       <c r="E60" t="s">
         <v>2</v>
       </c>
       <c r="F60">
         <v>8</v>
       </c>
-      <c r="H60">
-        <v>30</v>
-      </c>
-      <c r="I60" t="s">
-        <v>2</v>
-      </c>
-      <c r="J60">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>58</v>
       </c>
@@ -1916,7 +2010,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>59</v>
       </c>
@@ -1930,7 +2024,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B63">
         <v>60</v>
       </c>
@@ -1944,7 +2038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>61</v>
       </c>
@@ -2006,9 +2100,6 @@
       <sortCondition ref="H4:H67"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="1">
-    <mergeCell ref="B2:G2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5915FD65-CF20-42BF-982C-EEB5124332F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211F2869-FBDD-4139-91D1-9413E8B1A88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="91">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -1732,43 +1732,70 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="D44" t="s">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="E44" t="s">
         <v>2</v>
       </c>
       <c r="F44">
+        <v>8</v>
+      </c>
+      <c r="H44">
+        <v>41</v>
+      </c>
+      <c r="I44" t="s">
+        <v>2</v>
+      </c>
+      <c r="J44">
         <v>8</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E45" t="s">
         <v>2</v>
       </c>
       <c r="F45">
         <v>8</v>
+      </c>
+      <c r="H45">
+        <v>42</v>
+      </c>
+      <c r="I45" t="s">
+        <v>2</v>
+      </c>
+      <c r="J45">
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D46" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="E46" t="s">
         <v>2</v>
       </c>
       <c r="F46">
+        <v>8</v>
+      </c>
+      <c r="H46">
+        <v>43</v>
+      </c>
+      <c r="I46" t="s">
+        <v>2</v>
+      </c>
+      <c r="J46">
         <v>8</v>
       </c>
     </row>
@@ -1791,35 +1818,45 @@
       <c r="G47" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="2"/>
+      <c r="H47" s="2">
+        <v>44</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J47">
+        <v>8</v>
+      </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="2">
-        <v>5</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="B48">
+        <v>48</v>
+      </c>
+      <c r="D48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2</v>
+      </c>
+      <c r="F48">
+        <v>8</v>
+      </c>
+      <c r="H48">
+        <v>45</v>
+      </c>
+      <c r="I48" t="s">
+        <v>2</v>
+      </c>
+      <c r="J48">
         <v>9</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" s="2">
-        <v>2</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H48" s="2"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E49" t="s">
         <v>2</v>
@@ -1829,27 +1866,25 @@
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="8">
-        <v>7</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="D50" t="s">
+        <v>3</v>
+      </c>
+      <c r="E50" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50">
+        <v>8</v>
+      </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B51">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E51" t="s">
         <v>2</v>
@@ -1859,25 +1894,32 @@
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B52">
-        <v>14</v>
-      </c>
-      <c r="D52" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" t="s">
-        <v>2</v>
-      </c>
-      <c r="F52">
-        <v>8</v>
-      </c>
+      <c r="B52" s="2">
+        <v>5</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F52" s="2">
+        <v>2</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="2"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B53">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
         <v>2</v>
@@ -1887,25 +1929,27 @@
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B54">
-        <v>23</v>
-      </c>
-      <c r="D54" t="s">
-        <v>30</v>
-      </c>
-      <c r="E54" t="s">
-        <v>2</v>
-      </c>
-      <c r="F54">
-        <v>8</v>
-      </c>
+      <c r="B54" s="8">
+        <v>7</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B55">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E55" t="s">
         <v>2</v>
@@ -1915,30 +1959,25 @@
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B56" s="2">
-        <v>26</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" s="2">
-        <v>2</v>
-      </c>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
+      <c r="B56">
+        <v>14</v>
+      </c>
+      <c r="D56" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" t="s">
+        <v>2</v>
+      </c>
+      <c r="F56">
+        <v>8</v>
+      </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
         <v>2</v>
@@ -1949,10 +1988,10 @@
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B58">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D58" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E58" t="s">
         <v>2</v>
@@ -1962,32 +2001,30 @@
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B59" s="3">
-        <v>44</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E59" s="3" t="s">
+      <c r="B59" s="2">
+        <v>26</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F59" s="3">
-        <v>2</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H59" s="3"/>
+      <c r="F59" s="2">
+        <v>2</v>
+      </c>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B60">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D60" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E60" t="s">
         <v>2</v>
@@ -1998,10 +2035,10 @@
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B61">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="D61" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="E61" t="s">
         <v>2</v>
@@ -2011,67 +2048,74 @@
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B62">
-        <v>59</v>
-      </c>
-      <c r="D62" t="s">
-        <v>69</v>
-      </c>
-      <c r="E62" t="s">
-        <v>2</v>
-      </c>
-      <c r="F62">
-        <v>7</v>
-      </c>
+      <c r="B62" s="3">
+        <v>44</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F62" s="3">
+        <v>2</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H62" s="3"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B63">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E63" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B64">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E64" t="s">
         <v>2</v>
       </c>
       <c r="F64">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B65">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D65" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E65" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F65">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D66" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E66" t="s">
         <v>2</v>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211F2869-FBDD-4139-91D1-9413E8B1A88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BCE4971-C3F7-447C-955E-1B75002496AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>el 40% se hizo con IA</t>
+  </si>
+  <si>
+    <t>Utilizo 80% IA</t>
   </si>
 </sst>
 </file>
@@ -1851,7 +1854,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49">
         <v>1</v>
       </c>
@@ -1864,8 +1867,17 @@
       <c r="F49">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H49">
+        <v>48</v>
+      </c>
+      <c r="I49" t="s">
+        <v>2</v>
+      </c>
+      <c r="J49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50">
         <v>2</v>
       </c>
@@ -1879,7 +1891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51">
         <v>3</v>
       </c>
@@ -1892,8 +1904,17 @@
       <c r="F51">
         <v>8</v>
       </c>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H51">
+        <v>47</v>
+      </c>
+      <c r="I51" t="s">
+        <v>2</v>
+      </c>
+      <c r="J51">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="2">
         <v>5</v>
       </c>
@@ -1914,7 +1935,7 @@
       </c>
       <c r="H52" s="2"/>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>6</v>
       </c>
@@ -1928,7 +1949,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="8">
         <v>7</v>
       </c>
@@ -1944,7 +1965,7 @@
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>11</v>
       </c>
@@ -1958,7 +1979,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>14</v>
       </c>
@@ -1971,8 +1992,17 @@
       <c r="F56">
         <v>8</v>
       </c>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H56">
+        <v>49</v>
+      </c>
+      <c r="I56" t="s">
+        <v>2</v>
+      </c>
+      <c r="J56">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>17</v>
       </c>
@@ -1986,7 +2016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58">
         <v>23</v>
       </c>
@@ -2000,7 +2030,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="2">
         <v>26</v>
       </c>
@@ -2019,7 +2049,7 @@
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>30</v>
       </c>
@@ -2033,7 +2063,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>35</v>
       </c>
@@ -2047,7 +2077,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="3">
         <v>44</v>
       </c>
@@ -2068,7 +2098,7 @@
       </c>
       <c r="H62" s="3"/>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63">
         <v>58</v>
       </c>
@@ -2082,7 +2112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>59</v>
       </c>
@@ -2096,7 +2126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65">
         <v>60</v>
       </c>
@@ -2109,8 +2139,20 @@
       <c r="F65">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="H65">
+        <v>46</v>
+      </c>
+      <c r="I65" t="s">
+        <v>6</v>
+      </c>
+      <c r="J65">
+        <v>2</v>
+      </c>
+      <c r="K65" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>61</v>
       </c>
@@ -2124,7 +2166,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>64</v>
       </c>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BCE4971-C3F7-447C-955E-1B75002496AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AF5303-F3B0-43FA-8EA0-9B05FDFF7423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="97">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -304,6 +304,21 @@
   </si>
   <si>
     <t>Utilizo 80% IA</t>
+  </si>
+  <si>
+    <t>Costilla, Marita</t>
+  </si>
+  <si>
+    <t>NO PRESENTO</t>
+  </si>
+  <si>
+    <t>Balconte, Aldo Exequiel</t>
+  </si>
+  <si>
+    <t>Andrada, Fernando Exequiel</t>
+  </si>
+  <si>
+    <t>Romero, Nelson Daniel</t>
   </si>
 </sst>
 </file>
@@ -409,7 +424,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -690,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K67"/>
+  <dimension ref="B2:K71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
@@ -1854,305 +1869,329 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49">
+        <v>60</v>
+      </c>
+      <c r="D49" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" t="s">
+        <v>6</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>46</v>
+      </c>
+      <c r="I49" t="s">
+        <v>6</v>
+      </c>
+      <c r="J49">
+        <v>2</v>
+      </c>
+      <c r="K49" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>3</v>
+      </c>
+      <c r="D50" t="s">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50">
+        <v>8</v>
+      </c>
+      <c r="H50">
+        <v>47</v>
+      </c>
+      <c r="I50" t="s">
+        <v>2</v>
+      </c>
+      <c r="J50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B51">
         <v>1</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D51" t="s">
         <v>0</v>
       </c>
-      <c r="E49" t="s">
-        <v>2</v>
-      </c>
-      <c r="F49">
-        <v>8</v>
-      </c>
-      <c r="H49">
+      <c r="E51" t="s">
+        <v>2</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+      <c r="H51">
         <v>48</v>
       </c>
-      <c r="I49" t="s">
-        <v>2</v>
-      </c>
-      <c r="J49">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50">
-        <v>2</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="I51" t="s">
+        <v>2</v>
+      </c>
+      <c r="J51">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>14</v>
+      </c>
+      <c r="D52" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>8</v>
+      </c>
+      <c r="H52">
+        <v>49</v>
+      </c>
+      <c r="I52" t="s">
+        <v>2</v>
+      </c>
+      <c r="J52">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="D53" t="s">
         <v>3</v>
       </c>
-      <c r="E50" t="s">
-        <v>2</v>
-      </c>
-      <c r="F50">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51">
-        <v>3</v>
-      </c>
-      <c r="D51" t="s">
-        <v>4</v>
-      </c>
-      <c r="E51" t="s">
-        <v>2</v>
-      </c>
-      <c r="F51">
-        <v>8</v>
-      </c>
-      <c r="H51">
-        <v>47</v>
-      </c>
-      <c r="I51" t="s">
-        <v>2</v>
-      </c>
-      <c r="J51">
+      <c r="E53" t="s">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B54" s="2">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B52" s="2">
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F54" s="2">
+        <v>2</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <v>6</v>
+      </c>
+      <c r="D55" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55">
+        <v>8</v>
+      </c>
+      <c r="H55">
+        <v>53</v>
+      </c>
+      <c r="I55" t="s">
+        <v>2</v>
+      </c>
+      <c r="J55">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B56" s="8">
+        <v>7</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>11</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>2</v>
+      </c>
+      <c r="F57">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <v>17</v>
+      </c>
+      <c r="D58" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" t="s">
+        <v>2</v>
+      </c>
+      <c r="F58">
+        <v>8</v>
+      </c>
+      <c r="H58">
+        <v>50</v>
+      </c>
+      <c r="I58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B59">
+        <v>23</v>
+      </c>
+      <c r="D59" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" t="s">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B60" s="2">
+        <v>26</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F60" s="2">
+        <v>2</v>
+      </c>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <v>30</v>
+      </c>
+      <c r="D61" t="s">
+        <v>37</v>
+      </c>
+      <c r="E61" t="s">
+        <v>2</v>
+      </c>
+      <c r="F61">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B62">
+        <v>35</v>
+      </c>
+      <c r="D62" t="s">
+        <v>43</v>
+      </c>
+      <c r="E62" t="s">
+        <v>2</v>
+      </c>
+      <c r="F62">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B63" s="3">
+        <v>44</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F63" s="3">
+        <v>2</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B64">
+        <v>58</v>
+      </c>
+      <c r="D64" t="s">
+        <v>68</v>
+      </c>
+      <c r="E64" t="s">
+        <v>2</v>
+      </c>
+      <c r="F64">
+        <v>8</v>
+      </c>
+      <c r="H64">
+        <v>51</v>
+      </c>
+      <c r="I64" t="s">
+        <v>2</v>
+      </c>
+      <c r="J64">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65">
+        <v>59</v>
+      </c>
+      <c r="D65" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" t="s">
+        <v>2</v>
+      </c>
+      <c r="F65">
         <v>7</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" s="2">
-        <v>2</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H52" s="2"/>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53">
-        <v>6</v>
-      </c>
-      <c r="D53" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" t="s">
-        <v>2</v>
-      </c>
-      <c r="F53">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="8">
-        <v>7</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B55">
-        <v>11</v>
-      </c>
-      <c r="D55" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" t="s">
-        <v>2</v>
-      </c>
-      <c r="F55">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B56">
-        <v>14</v>
-      </c>
-      <c r="D56" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56" t="s">
-        <v>2</v>
-      </c>
-      <c r="F56">
-        <v>8</v>
-      </c>
-      <c r="H56">
-        <v>49</v>
-      </c>
-      <c r="I56" t="s">
-        <v>2</v>
-      </c>
-      <c r="J56">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57">
-        <v>17</v>
-      </c>
-      <c r="D57" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" t="s">
-        <v>2</v>
-      </c>
-      <c r="F57">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58">
-        <v>23</v>
-      </c>
-      <c r="D58" t="s">
-        <v>30</v>
-      </c>
-      <c r="E58" t="s">
-        <v>2</v>
-      </c>
-      <c r="F58">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B59" s="2">
-        <v>26</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F59" s="2">
-        <v>2</v>
-      </c>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60">
-        <v>30</v>
-      </c>
-      <c r="D60" t="s">
-        <v>37</v>
-      </c>
-      <c r="E60" t="s">
-        <v>2</v>
-      </c>
-      <c r="F60">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B61">
-        <v>35</v>
-      </c>
-      <c r="D61" t="s">
-        <v>43</v>
-      </c>
-      <c r="E61" t="s">
-        <v>2</v>
-      </c>
-      <c r="F61">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B62" s="3">
-        <v>44</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H62" s="3"/>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B63">
-        <v>58</v>
-      </c>
-      <c r="D63" t="s">
-        <v>68</v>
-      </c>
-      <c r="E63" t="s">
-        <v>2</v>
-      </c>
-      <c r="F63">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64">
-        <v>59</v>
-      </c>
-      <c r="D64" t="s">
-        <v>69</v>
-      </c>
-      <c r="E64" t="s">
-        <v>2</v>
-      </c>
-      <c r="F64">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B65">
-        <v>60</v>
-      </c>
-      <c r="D65" t="s">
-        <v>70</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65">
-        <v>2</v>
-      </c>
-      <c r="H65">
-        <v>46</v>
-      </c>
-      <c r="I65" t="s">
-        <v>6</v>
-      </c>
-      <c r="J65">
-        <v>2</v>
-      </c>
-      <c r="K65" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>61</v>
       </c>
@@ -2166,7 +2205,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>64</v>
       </c>
@@ -2178,6 +2217,95 @@
       </c>
       <c r="F67">
         <v>8</v>
+      </c>
+      <c r="H67">
+        <v>52</v>
+      </c>
+      <c r="I67" t="s">
+        <v>2</v>
+      </c>
+      <c r="J67">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68" t="s">
+        <v>93</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>54</v>
+      </c>
+      <c r="I68" t="s">
+        <v>2</v>
+      </c>
+      <c r="J68">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>94</v>
+      </c>
+      <c r="E69" t="s">
+        <v>93</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>55</v>
+      </c>
+      <c r="I69" t="s">
+        <v>2</v>
+      </c>
+      <c r="J69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>95</v>
+      </c>
+      <c r="E70" t="s">
+        <v>93</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>56</v>
+      </c>
+      <c r="I70" t="s">
+        <v>2</v>
+      </c>
+      <c r="J70">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>96</v>
+      </c>
+      <c r="E71" t="s">
+        <v>93</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>57</v>
+      </c>
+      <c r="I71" t="s">
+        <v>2</v>
+      </c>
+      <c r="J71">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BEED3D-71BC-4BDC-86D4-C855E971BFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3B9D6D-7E59-4B03-8F7A-1FB312DC53F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="115">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -361,6 +361,18 @@
   </si>
   <si>
     <t>Falto recuperar e Ingresar a los Input los valores</t>
+  </si>
+  <si>
+    <t>las funciones no deben devolver alert, prompt, ..</t>
+  </si>
+  <si>
+    <t>Excelente</t>
+  </si>
+  <si>
+    <t>Faltó guardar el estado y persistirlo</t>
+  </si>
+  <si>
+    <t>Faltaron estilos</t>
   </si>
 </sst>
 </file>
@@ -460,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -469,11 +481,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -773,7 +784,7 @@
     <col min="15" max="15" width="43.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>16</v>
       </c>
@@ -828,16 +839,16 @@
       <c r="K3" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="8" t="s">
         <v>107</v>
       </c>
     </row>
@@ -982,171 +993,216 @@
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
-      <c r="C8" s="5" t="s">
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <v>40</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>9</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>9</v>
+      </c>
+      <c r="O8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>7</v>
+      </c>
+      <c r="L9">
+        <v>6</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>10</v>
+      </c>
+      <c r="O9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="H10">
+        <v>20</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>7</v>
+      </c>
+      <c r="L10">
+        <v>7</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>5</v>
+      </c>
+      <c r="O10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="H11">
+        <v>31</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>8</v>
+      </c>
+      <c r="L11">
+        <v>8</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>10</v>
+      </c>
+      <c r="O11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="H12">
+        <v>37</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>9</v>
+      </c>
+      <c r="L12">
+        <v>9</v>
+      </c>
+      <c r="M12" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>9</v>
+      </c>
+      <c r="O12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="3"/>
+      <c r="C13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D13" s="3">
         <v>31</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F13" s="3">
         <v>2</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8">
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13">
         <v>7</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C9" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9">
-        <v>54</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>8</v>
-      </c>
-      <c r="H9">
-        <v>2</v>
-      </c>
-      <c r="I9" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10">
-        <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>8</v>
-      </c>
-      <c r="H10">
-        <v>5</v>
-      </c>
-      <c r="I10" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11">
-        <v>22</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>8</v>
-      </c>
-      <c r="H11">
-        <v>6</v>
-      </c>
-      <c r="I11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>6</v>
-      </c>
-      <c r="K11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12">
-        <v>16</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>8</v>
-      </c>
-      <c r="H12">
-        <v>7</v>
-      </c>
-      <c r="I12" t="s">
-        <v>5</v>
-      </c>
-      <c r="J12">
-        <v>2</v>
-      </c>
-      <c r="K12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13">
-        <v>15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>8</v>
-      </c>
-      <c r="H13">
-        <v>8</v>
-      </c>
-      <c r="I13" t="s">
-        <v>5</v>
-      </c>
-      <c r="J13">
-        <v>2</v>
-      </c>
-      <c r="K13" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D14">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
         <v>1</v>
@@ -1155,73 +1211,73 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I14" t="s">
         <v>1</v>
       </c>
       <c r="J14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15">
+        <v>28</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="I15" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="H16">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15">
-        <v>47</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>8</v>
-      </c>
-      <c r="H15">
-        <v>10</v>
-      </c>
-      <c r="I15" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16">
-        <v>55</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>8</v>
-      </c>
-      <c r="H16">
-        <v>11</v>
-      </c>
       <c r="I16" t="s">
         <v>1</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K16" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
+        <v>76</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
         <v>1</v>
@@ -1230,7 +1286,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I17" t="s">
         <v>5</v>
@@ -1239,41 +1295,44 @@
         <v>2</v>
       </c>
       <c r="K17" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
-        <v>60</v>
+      <c r="B18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="D18">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H18">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I18" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>13</v>
+      <c r="C19" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E19" t="s">
         <v>1</v>
@@ -1282,50 +1341,44 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I19" t="s">
         <v>1</v>
       </c>
       <c r="J19">
-        <v>7</v>
-      </c>
-      <c r="K19" t="s">
-        <v>81</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D20">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s">
         <v>1</v>
       </c>
       <c r="F20">
+        <v>8</v>
+      </c>
+      <c r="H20">
         <v>10</v>
       </c>
-      <c r="H20">
-        <v>15</v>
-      </c>
       <c r="I20" t="s">
         <v>1</v>
       </c>
       <c r="J20">
-        <v>10</v>
-      </c>
-      <c r="K20" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="D21">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="E21" t="s">
         <v>1</v>
@@ -1334,7 +1387,7 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I21" t="s">
         <v>1</v>
@@ -1342,13 +1395,19 @@
       <c r="J21">
         <v>7</v>
       </c>
+      <c r="K21" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>80</v>
+      </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
         <v>1</v>
@@ -1357,44 +1416,50 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I22" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D23">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E23" t="s">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I23" t="s">
         <v>1</v>
       </c>
       <c r="J23">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="K23" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D24">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E24" t="s">
         <v>1</v>
@@ -1403,70 +1468,73 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I24" t="s">
         <v>1</v>
       </c>
       <c r="J24">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="K24" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D25">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H25">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I25" t="s">
         <v>1</v>
       </c>
       <c r="J25">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="K25" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="D26">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="E26" t="s">
         <v>1</v>
       </c>
       <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="H26">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26">
         <v>7</v>
-      </c>
-      <c r="H26">
-        <v>21</v>
-      </c>
-      <c r="I26" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>8</v>
-      </c>
-      <c r="K26" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D27">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E27" t="s">
         <v>1</v>
@@ -1475,24 +1543,21 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27">
         <v>5</v>
-      </c>
-      <c r="J27">
-        <v>2</v>
-      </c>
-      <c r="K27" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D28">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E28" t="s">
         <v>1</v>
@@ -1501,53 +1566,47 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I28" t="s">
         <v>1</v>
       </c>
       <c r="J28">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>10</v>
+      <c r="C29" t="s">
+        <v>65</v>
       </c>
       <c r="D29">
-        <v>12</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="2">
-        <v>2</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" s="2">
-        <v>24</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>5</v>
+        <v>57</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>7</v>
+      </c>
+      <c r="H29">
+        <v>21</v>
+      </c>
+      <c r="I29" t="s">
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K29" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D30">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
         <v>1</v>
@@ -1556,21 +1615,24 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="K30" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D31">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s">
         <v>1</v>
@@ -1579,7 +1641,7 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I31" t="s">
         <v>1</v>
@@ -1589,66 +1651,66 @@
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C32" t="s">
+      <c r="B32" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32">
+        <v>12</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="2">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="2">
         <v>24</v>
       </c>
-      <c r="D32">
-        <v>19</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32">
-        <v>8</v>
-      </c>
-      <c r="H32">
-        <v>27</v>
-      </c>
-      <c r="I32" t="s">
-        <v>1</v>
+      <c r="I32" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="K32" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>17</v>
+      <c r="C33" t="s">
+        <v>40</v>
       </c>
       <c r="D33">
-        <v>13</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="2">
-        <v>2</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H33" s="2">
-        <v>29</v>
-      </c>
-      <c r="I33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+      <c r="H33">
+        <v>25</v>
+      </c>
+      <c r="I33" t="s">
         <v>1</v>
       </c>
       <c r="J33">
-        <v>2</v>
-      </c>
-      <c r="K33" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D34">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E34" t="s">
         <v>1</v>
@@ -1657,21 +1719,21 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I34" t="s">
         <v>1</v>
       </c>
       <c r="J34">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D35">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E35" t="s">
         <v>1</v>
@@ -1680,44 +1742,53 @@
         <v>8</v>
       </c>
       <c r="H35">
+        <v>27</v>
+      </c>
+      <c r="I35" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I35" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C36" t="s">
-        <v>58</v>
+      <c r="C36" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D36">
-        <v>50</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36">
-        <v>8</v>
-      </c>
-      <c r="H36">
-        <v>32</v>
-      </c>
-      <c r="I36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" s="2">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="2">
+        <v>29</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>1</v>
       </c>
       <c r="J36">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="D37">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E37" t="s">
         <v>1</v>
@@ -1726,24 +1797,21 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I37" t="s">
         <v>1</v>
       </c>
       <c r="J37">
-        <v>6</v>
-      </c>
-      <c r="K37" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D38">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E38" t="s">
         <v>1</v>
@@ -1752,7 +1820,7 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I38" t="s">
         <v>1</v>
@@ -1763,10 +1831,10 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D39">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E39" t="s">
         <v>1</v>
@@ -1775,21 +1843,24 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I39" t="s">
         <v>1</v>
       </c>
       <c r="J39">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="K39" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D40">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E40" t="s">
         <v>1</v>
@@ -1798,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="H40">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I40" t="s">
         <v>1</v>
@@ -1809,42 +1880,42 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D41">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E41" t="s">
         <v>1</v>
       </c>
       <c r="F41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H41">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I41" t="s">
         <v>1</v>
       </c>
       <c r="J41">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D42">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="H42">
         <v>36</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42">
-        <v>8</v>
-      </c>
-      <c r="H42">
-        <v>38</v>
       </c>
       <c r="I42" t="s">
         <v>1</v>
@@ -1855,10 +1926,10 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E43" t="s">
         <v>1</v>
@@ -1867,7 +1938,7 @@
         <v>8</v>
       </c>
       <c r="H43">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I43" t="s">
         <v>1</v>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3B9D6D-7E59-4B03-8F7A-1FB312DC53F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4410FD65-B2C2-4EEE-9002-CD3D71BBBA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="118">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -373,6 +373,15 @@
   </si>
   <si>
     <t>Faltaron estilos</t>
+  </si>
+  <si>
+    <t>No guardó el estado de la aplicación en el localStorage</t>
+  </si>
+  <si>
+    <t>Faltaron estilos y no se encerro todo el bloque dentro de window.onload</t>
+  </si>
+  <si>
+    <t>Faltan estilos, falta el window.onload, …</t>
   </si>
 </sst>
 </file>
@@ -779,7 +788,7 @@
     <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="50.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" customWidth="1"/>
     <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="43.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1168,41 +1177,46 @@
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="3">
-        <v>31</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="3">
-        <v>2</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>8</v>
+      </c>
+      <c r="H13">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
         <v>1</v>
       </c>
       <c r="J13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>10</v>
+      </c>
+      <c r="M13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N13">
         <v>7</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>73</v>
+      <c r="O13" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C14" s="5" t="s">
-        <v>62</v>
+      <c r="C14" t="s">
+        <v>56</v>
       </c>
       <c r="D14">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
         <v>1</v>
@@ -1211,21 +1225,33 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s">
         <v>1</v>
       </c>
       <c r="J14">
         <v>9</v>
+      </c>
+      <c r="L14">
+        <v>11</v>
+      </c>
+      <c r="M14" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>8</v>
+      </c>
+      <c r="O14" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C15" s="5" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="D15">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s">
         <v>1</v>
@@ -1234,151 +1260,214 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I15" t="s">
         <v>1</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="L15">
+        <v>12</v>
+      </c>
+      <c r="M15" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>8</v>
+      </c>
+      <c r="O15" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C16" s="5" t="s">
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16">
+        <v>19</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="H16">
         <v>27</v>
       </c>
-      <c r="D16">
-        <v>22</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>8</v>
-      </c>
-      <c r="H16">
-        <v>6</v>
-      </c>
       <c r="I16" t="s">
         <v>1</v>
       </c>
       <c r="J16">
-        <v>6</v>
-      </c>
-      <c r="K16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>20</v>
+        <v>7</v>
+      </c>
+      <c r="L16">
+        <v>13</v>
+      </c>
+      <c r="M16" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>7</v>
+      </c>
+      <c r="O16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>60</v>
       </c>
       <c r="D17">
+        <v>52</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>9</v>
+      </c>
+      <c r="H17">
+        <v>13</v>
+      </c>
+      <c r="I17" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>7</v>
+      </c>
+      <c r="K17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L17">
+        <v>14</v>
+      </c>
+      <c r="M17" t="s">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>9</v>
+      </c>
+      <c r="O17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>8</v>
+      </c>
+      <c r="H18">
+        <v>14</v>
+      </c>
+      <c r="I18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>7</v>
+      </c>
+      <c r="K18" t="s">
+        <v>81</v>
+      </c>
+      <c r="L18">
+        <v>15</v>
+      </c>
+      <c r="M18" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>8</v>
+      </c>
+      <c r="O18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19">
+        <v>45</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>10</v>
+      </c>
+      <c r="H19">
+        <v>15</v>
+      </c>
+      <c r="I19" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>10</v>
+      </c>
+      <c r="K19" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19">
         <v>16</v>
       </c>
-      <c r="E17" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>8</v>
-      </c>
-      <c r="H17">
+      <c r="M19" t="s">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>8</v>
+      </c>
+      <c r="H20">
+        <v>36</v>
+      </c>
+      <c r="I20" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>9</v>
+      </c>
+      <c r="L20">
+        <v>17</v>
+      </c>
+      <c r="M20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N20">
         <v>7</v>
       </c>
-      <c r="I17" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17">
-        <v>2</v>
-      </c>
-      <c r="K17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18">
-        <v>15</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>8</v>
-      </c>
-      <c r="H18">
-        <v>8</v>
-      </c>
-      <c r="I18" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18">
-        <v>2</v>
-      </c>
-      <c r="K18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C19" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19">
-        <v>21</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>8</v>
-      </c>
-      <c r="H19">
-        <v>9</v>
-      </c>
-      <c r="I19" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20">
-        <v>47</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20">
-        <v>8</v>
-      </c>
-      <c r="H20">
-        <v>10</v>
-      </c>
-      <c r="I20" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="O20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="D21">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="E21" t="s">
         <v>1</v>
@@ -1387,7 +1476,7 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I21" t="s">
         <v>1</v>
@@ -1395,19 +1484,25 @@
       <c r="J21">
         <v>7</v>
       </c>
-      <c r="K21" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
+      <c r="L21">
+        <v>18</v>
+      </c>
+      <c r="M21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>9</v>
+      </c>
+      <c r="O21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E22" t="s">
         <v>1</v>
@@ -1416,278 +1511,306 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22">
         <v>5</v>
       </c>
-      <c r="J22">
+      <c r="L22">
+        <v>19</v>
+      </c>
+      <c r="M22" t="s">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>9</v>
+      </c>
+      <c r="O22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>8</v>
+      </c>
+      <c r="H23">
+        <v>23</v>
+      </c>
+      <c r="I23" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>8</v>
+      </c>
+      <c r="L23">
+        <v>20</v>
+      </c>
+      <c r="M23" t="s">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>9</v>
+      </c>
+      <c r="O23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B24" s="3"/>
+      <c r="C24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="3">
+        <v>31</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
         <v>2</v>
       </c>
-      <c r="K22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23">
-        <v>52</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <v>9</v>
-      </c>
-      <c r="H23">
-        <v>13</v>
-      </c>
-      <c r="I23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>7</v>
-      </c>
-      <c r="K23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24">
-        <v>10</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>8</v>
-      </c>
-      <c r="H24">
-        <v>14</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="G24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>1</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
-      <c r="K24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
-        <v>53</v>
+      <c r="K24" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C25" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="D25">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s">
         <v>1</v>
       </c>
       <c r="F25">
+        <v>8</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26">
+        <v>22</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="H26">
+        <v>6</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>6</v>
+      </c>
+      <c r="K26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27">
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>8</v>
+      </c>
+      <c r="H27">
+        <v>7</v>
+      </c>
+      <c r="I27" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>8</v>
+      </c>
+      <c r="H28">
+        <v>8</v>
+      </c>
+      <c r="I28" t="s">
+        <v>5</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C29" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29">
+        <v>21</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>8</v>
+      </c>
+      <c r="H29">
+        <v>9</v>
+      </c>
+      <c r="I29" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30">
+        <v>47</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
+      </c>
+      <c r="H30">
         <v>10</v>
       </c>
-      <c r="H25">
-        <v>15</v>
-      </c>
-      <c r="I25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>10</v>
-      </c>
-      <c r="K25" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26">
-        <v>27</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>8</v>
-      </c>
-      <c r="H26">
-        <v>16</v>
-      </c>
-      <c r="I26" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26">
+      <c r="I30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27">
-        <v>33</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>8</v>
-      </c>
-      <c r="H27">
-        <v>18</v>
-      </c>
-      <c r="I27" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C28" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28">
-        <v>41</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <v>8</v>
-      </c>
-      <c r="H28">
-        <v>19</v>
-      </c>
-      <c r="I28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29">
-        <v>57</v>
-      </c>
-      <c r="E29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31">
+        <v>55</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>8</v>
+      </c>
+      <c r="H31">
+        <v>11</v>
+      </c>
+      <c r="I31" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31">
         <v>7</v>
       </c>
-      <c r="H29">
-        <v>21</v>
-      </c>
-      <c r="I29" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29">
-        <v>8</v>
-      </c>
-      <c r="K29" t="s">
+      <c r="K31" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30">
-        <v>38</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <v>8</v>
-      </c>
-      <c r="H30">
-        <v>22</v>
-      </c>
-      <c r="I30" t="s">
-        <v>5</v>
-      </c>
-      <c r="J30">
-        <v>2</v>
-      </c>
-      <c r="K30" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31">
-        <v>24</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <v>8</v>
-      </c>
-      <c r="H31">
-        <v>23</v>
-      </c>
-      <c r="I31" t="s">
-        <v>1</v>
-      </c>
-      <c r="J31">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>10</v>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
       </c>
       <c r="D32">
+        <v>8</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>8</v>
+      </c>
+      <c r="H32">
         <v>12</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="2">
-        <v>2</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" s="2">
-        <v>24</v>
-      </c>
-      <c r="I32" s="2" t="s">
+      <c r="I32" t="s">
         <v>5</v>
       </c>
       <c r="J32">
         <v>2</v>
       </c>
       <c r="K32" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D33">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E33" t="s">
         <v>1</v>
@@ -1696,7 +1819,7 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I33" t="s">
         <v>1</v>
@@ -1707,33 +1830,36 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D34">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E34" t="s">
         <v>1</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H34">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s">
         <v>1</v>
       </c>
       <c r="J34">
         <v>8</v>
+      </c>
+      <c r="K34" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D35">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
         <v>1</v>
@@ -1742,13 +1868,16 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I35" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J35">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="K35" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
@@ -1756,10 +1885,10 @@
         <v>31</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D36">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>5</v>
@@ -1771,24 +1900,24 @@
         <v>18</v>
       </c>
       <c r="H36" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>2</v>
       </c>
       <c r="K36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D37">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E37" t="s">
         <v>1</v>
@@ -1797,44 +1926,53 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I37" t="s">
         <v>1</v>
       </c>
       <c r="J37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38">
+        <v>13</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C38" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38">
-        <v>50</v>
-      </c>
-      <c r="E38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38">
-        <v>8</v>
-      </c>
-      <c r="H38">
-        <v>32</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="F38" s="2">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="2">
+        <v>29</v>
+      </c>
+      <c r="I38" s="2" t="s">
         <v>1</v>
       </c>
       <c r="J38">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="K38" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="D39">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E39" t="s">
         <v>1</v>
@@ -1843,24 +1981,21 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I39" t="s">
         <v>1</v>
       </c>
       <c r="J39">
-        <v>6</v>
-      </c>
-      <c r="K39" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D40">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E40" t="s">
         <v>1</v>
@@ -1869,7 +2004,7 @@
         <v>8</v>
       </c>
       <c r="H40">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I40" t="s">
         <v>1</v>
@@ -1880,10 +2015,10 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D41">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E41" t="s">
         <v>1</v>
@@ -1892,21 +2027,24 @@
         <v>8</v>
       </c>
       <c r="H41">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I41" t="s">
         <v>1</v>
       </c>
       <c r="J41">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="K41" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D42">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E42" t="s">
         <v>1</v>
@@ -1915,7 +2053,7 @@
         <v>8</v>
       </c>
       <c r="H42">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I42" t="s">
         <v>1</v>
@@ -1926,10 +2064,10 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D43">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E43" t="s">
         <v>1</v>
@@ -1938,21 +2076,21 @@
         <v>8</v>
       </c>
       <c r="H43">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I43" t="s">
         <v>1</v>
       </c>
       <c r="J43">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="D44">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="E44" t="s">
         <v>1</v>
@@ -1961,21 +2099,21 @@
         <v>8</v>
       </c>
       <c r="H44">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I44" t="s">
         <v>1</v>
       </c>
       <c r="J44">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D45">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s">
         <v>1</v>
@@ -1984,88 +2122,88 @@
         <v>8</v>
       </c>
       <c r="H45">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I45" t="s">
         <v>1</v>
       </c>
       <c r="J45">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46">
+        <v>25</v>
+      </c>
+      <c r="E46" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>8</v>
+      </c>
+      <c r="H46">
+        <v>42</v>
+      </c>
+      <c r="I46" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
         <v>70</v>
       </c>
-      <c r="D46">
+      <c r="D47">
         <v>62</v>
       </c>
-      <c r="E46" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46">
-        <v>8</v>
-      </c>
-      <c r="H46">
+      <c r="E47" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>8</v>
+      </c>
+      <c r="H47">
         <v>43</v>
       </c>
-      <c r="I46" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="I47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D48" s="2">
         <v>4</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F48" s="2">
         <v>2</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G48" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H48" s="2">
         <v>44</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48">
-        <v>48</v>
-      </c>
-      <c r="E48" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48">
-        <v>8</v>
-      </c>
-      <c r="H48">
-        <v>45</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="I48" s="2" t="s">
         <v>1</v>
       </c>
       <c r="J48">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4410FD65-B2C2-4EEE-9002-CD3D71BBBA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0BE0E4-C31B-4E7A-BB43-988B774F326E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="124">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -382,6 +382,24 @@
   </si>
   <si>
     <t>Faltan estilos, falta el window.onload, …</t>
+  </si>
+  <si>
+    <t>Falto misDatos.txt y los estilos</t>
+  </si>
+  <si>
+    <t>No puso estilos, no puso MisDatos.txt</t>
+  </si>
+  <si>
+    <t>Faltaron CSS</t>
+  </si>
+  <si>
+    <t>no tiene el modelo, pero la funcion esta dentro del controlador</t>
+  </si>
+  <si>
+    <t>Chaves Yance Jennifer Denis</t>
+  </si>
+  <si>
+    <t>100% hecho con IA</t>
   </si>
 </sst>
 </file>
@@ -774,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:O72"/>
+  <dimension ref="B2:O73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -1316,7 +1334,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>60</v>
       </c>
@@ -1354,7 +1372,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>13</v>
       </c>
@@ -1392,7 +1410,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>53</v>
       </c>
@@ -1427,7 +1445,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>23</v>
       </c>
@@ -1462,7 +1480,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>32</v>
       </c>
@@ -1497,7 +1515,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>39</v>
       </c>
@@ -1532,7 +1550,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>29</v>
       </c>
@@ -1567,204 +1585,260 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="3"/>
-      <c r="C24" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="3">
-        <v>31</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="3">
-        <v>2</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1</v>
-      </c>
-      <c r="I24" s="3" t="s">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24">
+        <v>47</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>8</v>
+      </c>
+      <c r="H24">
+        <v>10</v>
+      </c>
+      <c r="I24" t="s">
         <v>1</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C25" s="5" t="s">
+      <c r="L24">
+        <v>21</v>
+      </c>
+      <c r="M24" t="s">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>9</v>
+      </c>
+      <c r="O24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25">
+        <v>36</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>8</v>
+      </c>
+      <c r="H25">
+        <v>38</v>
+      </c>
+      <c r="I25" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>9</v>
+      </c>
+      <c r="L25">
+        <v>22</v>
+      </c>
+      <c r="M25" t="s">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>9</v>
+      </c>
+      <c r="O25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C26" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D25">
+      <c r="D26">
         <v>28</v>
       </c>
-      <c r="E25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>8</v>
-      </c>
-      <c r="H25">
+      <c r="E26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="H26">
         <v>5</v>
       </c>
-      <c r="I25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C26" s="5" t="s">
+      <c r="I26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>8</v>
+      </c>
+      <c r="L26">
+        <v>23</v>
+      </c>
+      <c r="M26" t="s">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>9</v>
+      </c>
+      <c r="O26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27">
+        <v>21</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>8</v>
+      </c>
+      <c r="H27">
+        <v>9</v>
+      </c>
+      <c r="I27" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>6</v>
+      </c>
+      <c r="L27">
+        <v>24</v>
+      </c>
+      <c r="M27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>8</v>
+      </c>
+      <c r="O27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28">
+        <v>50</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>8</v>
+      </c>
+      <c r="H28">
+        <v>32</v>
+      </c>
+      <c r="I28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>9</v>
+      </c>
+      <c r="L28">
+        <v>25</v>
+      </c>
+      <c r="M28" t="s">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29">
+        <v>39</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>8</v>
+      </c>
+      <c r="H29">
+        <v>26</v>
+      </c>
+      <c r="I29" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>8</v>
+      </c>
+      <c r="L29">
+        <v>26</v>
+      </c>
+      <c r="M29" t="s">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>9</v>
+      </c>
+      <c r="O29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30">
+        <v>40</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
+      </c>
+      <c r="H30">
+        <v>34</v>
+      </c>
+      <c r="I30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>9</v>
+      </c>
+      <c r="L30">
         <v>27</v>
       </c>
-      <c r="D26">
-        <v>22</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>8</v>
-      </c>
-      <c r="H26">
-        <v>6</v>
-      </c>
-      <c r="I26" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>6</v>
-      </c>
-      <c r="K26" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27">
-        <v>16</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>8</v>
-      </c>
-      <c r="H27">
-        <v>7</v>
-      </c>
-      <c r="I27" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27">
-        <v>2</v>
-      </c>
-      <c r="K27" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28">
-        <v>15</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <v>8</v>
-      </c>
-      <c r="H28">
-        <v>8</v>
-      </c>
-      <c r="I28" t="s">
-        <v>5</v>
-      </c>
-      <c r="J28">
-        <v>2</v>
-      </c>
-      <c r="K28" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C29" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29">
-        <v>21</v>
-      </c>
-      <c r="E29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>8</v>
-      </c>
-      <c r="H29">
-        <v>9</v>
-      </c>
-      <c r="I29" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30">
-        <v>47</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <v>8</v>
-      </c>
-      <c r="H30">
-        <v>10</v>
-      </c>
-      <c r="I30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J30">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="M30" t="s">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>8</v>
+      </c>
+      <c r="O30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="E31" t="s">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="I31" t="s">
         <v>1</v>
@@ -1772,19 +1846,22 @@
       <c r="J31">
         <v>7</v>
       </c>
-      <c r="K31" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
+      <c r="L31">
+        <v>28</v>
+      </c>
+      <c r="M31" t="s">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E32" t="s">
         <v>1</v>
@@ -1793,413 +1870,504 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="I32" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>7</v>
+      </c>
+      <c r="L32">
+        <v>29</v>
+      </c>
+      <c r="M32" t="s">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+      <c r="H33">
+        <v>48</v>
+      </c>
+      <c r="I33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>8</v>
+      </c>
+      <c r="L33">
+        <v>30</v>
+      </c>
+      <c r="M33" t="s">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>9</v>
+      </c>
+      <c r="O33" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B34" s="3"/>
+      <c r="C34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="3">
+        <v>31</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J32">
+      <c r="F34" s="3">
         <v>2</v>
       </c>
-      <c r="K32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C33" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33">
-        <v>41</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33">
-        <v>8</v>
-      </c>
-      <c r="H33">
+      <c r="G34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H34" s="3">
+        <v>1</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>7</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L34">
+        <v>31</v>
+      </c>
+      <c r="M34" t="s">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>9</v>
+      </c>
+      <c r="O34" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
         <v>19</v>
       </c>
-      <c r="I33" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C34" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34">
-        <v>57</v>
-      </c>
-      <c r="E34" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34">
+      <c r="D35">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>8</v>
+      </c>
+      <c r="H35">
+        <v>49</v>
+      </c>
+      <c r="I35" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>9</v>
+      </c>
+      <c r="L35">
+        <v>32</v>
+      </c>
+      <c r="M35" t="s">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>9</v>
+      </c>
+      <c r="O35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C36" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36">
+        <v>22</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>8</v>
+      </c>
+      <c r="H36">
+        <v>6</v>
+      </c>
+      <c r="I36" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>6</v>
+      </c>
+      <c r="K36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>16</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>8</v>
+      </c>
+      <c r="H37">
         <v>7</v>
       </c>
-      <c r="H34">
+      <c r="I37" t="s">
+        <v>5</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I34" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34">
-        <v>8</v>
-      </c>
-      <c r="K34" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35">
-        <v>38</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35">
-        <v>8</v>
-      </c>
-      <c r="H35">
-        <v>22</v>
-      </c>
-      <c r="I35" t="s">
+      <c r="D38">
+        <v>15</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>8</v>
+      </c>
+      <c r="H38">
+        <v>8</v>
+      </c>
+      <c r="I38" t="s">
         <v>5</v>
-      </c>
-      <c r="J35">
-        <v>2</v>
-      </c>
-      <c r="K35" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36">
-        <v>12</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" s="2">
-        <v>2</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="2">
-        <v>24</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J36">
-        <v>2</v>
-      </c>
-      <c r="K36" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C37" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37">
-        <v>39</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>8</v>
-      </c>
-      <c r="H37">
-        <v>26</v>
-      </c>
-      <c r="I37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38">
-        <v>13</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" s="2">
-        <v>2</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H38" s="2">
-        <v>29</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="J38">
         <v>2</v>
       </c>
       <c r="K38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39">
+        <v>55</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="H39">
+        <v>11</v>
+      </c>
+      <c r="I39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>7</v>
+      </c>
+      <c r="K39" t="s">
+        <v>78</v>
+      </c>
+      <c r="L39">
+        <v>33</v>
+      </c>
+      <c r="M39" t="s">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>6</v>
+      </c>
+      <c r="O39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40">
+        <v>8</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>8</v>
+      </c>
+      <c r="H40">
+        <v>12</v>
+      </c>
+      <c r="I40" t="s">
+        <v>5</v>
+      </c>
+      <c r="J40">
+        <v>2</v>
+      </c>
+      <c r="K40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41">
+        <v>41</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>8</v>
+      </c>
+      <c r="H41">
+        <v>19</v>
+      </c>
+      <c r="I41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42">
+        <v>57</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>7</v>
+      </c>
+      <c r="H42">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>8</v>
+      </c>
+      <c r="K42" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43">
+        <v>38</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+      <c r="H43">
+        <v>22</v>
+      </c>
+      <c r="I43" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44">
+        <v>12</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="2">
+        <v>2</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="2">
+        <v>24</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45">
+        <v>13</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="2">
+        <v>2</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="2">
+        <v>29</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>2</v>
+      </c>
+      <c r="K45" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C39" t="s">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
         <v>61</v>
       </c>
-      <c r="D39">
+      <c r="D46">
         <v>53</v>
       </c>
-      <c r="E39" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39">
-        <v>8</v>
-      </c>
-      <c r="H39">
+      <c r="E46" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>8</v>
+      </c>
+      <c r="H46">
         <v>30</v>
       </c>
-      <c r="I39" t="s">
-        <v>1</v>
-      </c>
-      <c r="J39">
+      <c r="I46" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C40" t="s">
-        <v>58</v>
-      </c>
-      <c r="D40">
-        <v>50</v>
-      </c>
-      <c r="E40" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40">
-        <v>8</v>
-      </c>
-      <c r="H40">
-        <v>32</v>
-      </c>
-      <c r="I40" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C41" t="s">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
         <v>25</v>
       </c>
-      <c r="D41">
+      <c r="D47">
         <v>20</v>
       </c>
-      <c r="E41" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41">
-        <v>8</v>
-      </c>
-      <c r="H41">
+      <c r="E47" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>8</v>
+      </c>
+      <c r="H47">
         <v>33</v>
       </c>
-      <c r="I41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41">
+      <c r="I47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47">
         <v>6</v>
       </c>
-      <c r="K41" t="s">
+      <c r="K47" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C42" t="s">
-        <v>46</v>
-      </c>
-      <c r="D42">
-        <v>40</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42">
-        <v>8</v>
-      </c>
-      <c r="H42">
+      <c r="L47">
+        <v>35</v>
+      </c>
+      <c r="M47" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+      <c r="O47" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
         <v>34</v>
       </c>
-      <c r="I42" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C43" t="s">
-        <v>34</v>
-      </c>
-      <c r="D43">
+      <c r="D48">
         <v>29</v>
       </c>
-      <c r="E43" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43">
-        <v>8</v>
-      </c>
-      <c r="H43">
+      <c r="E48" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>8</v>
+      </c>
+      <c r="H48">
         <v>35</v>
       </c>
-      <c r="I43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C44" t="s">
-        <v>42</v>
-      </c>
-      <c r="D44">
-        <v>36</v>
-      </c>
-      <c r="E44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>8</v>
-      </c>
-      <c r="H44">
-        <v>38</v>
-      </c>
-      <c r="I44" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C45" t="s">
-        <v>71</v>
-      </c>
-      <c r="D45">
-        <v>63</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45">
-        <v>8</v>
-      </c>
-      <c r="H45">
-        <v>41</v>
-      </c>
-      <c r="I45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C46" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46">
-        <v>25</v>
-      </c>
-      <c r="E46" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46">
-        <v>8</v>
-      </c>
-      <c r="H46">
-        <v>42</v>
-      </c>
-      <c r="I46" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C47" t="s">
-        <v>70</v>
-      </c>
-      <c r="D47">
-        <v>62</v>
-      </c>
-      <c r="E47" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47">
-        <v>8</v>
-      </c>
-      <c r="H47">
-        <v>43</v>
-      </c>
-      <c r="I47" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" s="2">
-        <v>4</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" s="2">
-        <v>2</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H48" s="2">
-        <v>44</v>
-      </c>
-      <c r="I48" s="2" t="s">
+      <c r="I48" t="s">
         <v>1</v>
       </c>
       <c r="J48">
@@ -2208,36 +2376,33 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D49">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E49" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H49">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I49" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J49">
-        <v>2</v>
-      </c>
-      <c r="K49" t="s">
-        <v>87</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E50" t="s">
         <v>1</v>
@@ -2246,21 +2411,21 @@
         <v>8</v>
       </c>
       <c r="H50">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I50" t="s">
         <v>1</v>
       </c>
       <c r="J50">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="E51" t="s">
         <v>1</v>
@@ -2269,7 +2434,7 @@
         <v>8</v>
       </c>
       <c r="H51">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I51" t="s">
         <v>1</v>
@@ -2279,54 +2444,66 @@
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52">
-        <v>14</v>
-      </c>
-      <c r="E52" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52">
-        <v>8</v>
-      </c>
-      <c r="H52">
-        <v>49</v>
-      </c>
-      <c r="I52" t="s">
+      <c r="B52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="2">
+        <v>4</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="2">
+        <v>2</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H52" s="2">
+        <v>44</v>
+      </c>
+      <c r="I52" s="2" t="s">
         <v>1</v>
       </c>
       <c r="J52">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C53" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D53">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="E53" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F53">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I53" t="s">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J53">
+        <v>2</v>
+      </c>
+      <c r="K53" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D54">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="E54" t="s">
         <v>1</v>
@@ -2335,21 +2512,18 @@
         <v>8</v>
       </c>
       <c r="H54">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I54" t="s">
         <v>1</v>
-      </c>
-      <c r="J54">
-        <v>9</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D55">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E55" t="s">
         <v>1</v>
@@ -2358,7 +2532,7 @@
         <v>8</v>
       </c>
       <c r="H55">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I55" t="s">
         <v>1</v>
@@ -2369,10 +2543,10 @@
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="D56">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="E56" t="s">
         <v>1</v>
@@ -2381,7 +2555,7 @@
         <v>8</v>
       </c>
       <c r="H56">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I56" t="s">
         <v>1</v>
@@ -2392,16 +2566,19 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
-        <v>88</v>
+        <v>9</v>
+      </c>
+      <c r="D57">
+        <v>6</v>
       </c>
       <c r="E57" t="s">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H57">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I57" t="s">
         <v>1</v>
@@ -2412,7 +2589,7 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E58" t="s">
         <v>89</v>
@@ -2421,18 +2598,18 @@
         <v>0</v>
       </c>
       <c r="H58">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I58" t="s">
         <v>1</v>
       </c>
       <c r="J58">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E59" t="s">
         <v>89</v>
@@ -2441,18 +2618,18 @@
         <v>0</v>
       </c>
       <c r="H59">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I59" t="s">
         <v>1</v>
       </c>
       <c r="J59">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E60" t="s">
         <v>89</v>
@@ -2461,13 +2638,13 @@
         <v>0</v>
       </c>
       <c r="H60">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I60" t="s">
         <v>1</v>
       </c>
       <c r="J60">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
@@ -2535,7 +2712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C65" t="s">
         <v>28</v>
       </c>
@@ -2549,7 +2726,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
         <v>8</v>
       </c>
@@ -2568,7 +2745,7 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>35</v>
       </c>
@@ -2582,7 +2759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
         <v>41</v>
       </c>
@@ -2596,7 +2773,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B69" s="3" t="s">
         <v>51</v>
       </c>
@@ -2617,7 +2794,7 @@
       </c>
       <c r="H69" s="3"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>67</v>
       </c>
@@ -2631,7 +2808,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
         <v>69</v>
       </c>
@@ -2654,7 +2831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C72" t="s">
         <v>93</v>
       </c>
@@ -2666,6 +2843,20 @@
       </c>
       <c r="J72">
         <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>122</v>
+      </c>
+      <c r="L73">
+        <v>34</v>
+      </c>
+      <c r="M73" t="s">
+        <v>1</v>
+      </c>
+      <c r="N73">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0BE0E4-C31B-4E7A-BB43-988B774F326E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E66518C-121B-43A8-9EF4-3A23026B81B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="129">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -400,6 +400,21 @@
   </si>
   <si>
     <t>100% hecho con IA</t>
+  </si>
+  <si>
+    <t>Malak Aragón Santiago</t>
+  </si>
+  <si>
+    <t>80% utilizó IA</t>
+  </si>
+  <si>
+    <t>Ayala Nahuel</t>
+  </si>
+  <si>
+    <t>No Persistió los datos en el localStorage</t>
+  </si>
+  <si>
+    <t>Falta persistir en localStorage, en varios falta el estado de la aplicación</t>
   </si>
 </sst>
 </file>
@@ -792,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:O73"/>
+  <dimension ref="B2:O75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -1831,11 +1846,14 @@
       <c r="C31" t="s">
         <v>92</v>
       </c>
+      <c r="D31">
+        <v>67</v>
+      </c>
       <c r="E31" t="s">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H31">
         <v>57</v>
@@ -2001,136 +2019,160 @@
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C36" s="5" t="s">
+      <c r="C36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36">
+        <v>55</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>8</v>
+      </c>
+      <c r="H36">
+        <v>11</v>
+      </c>
+      <c r="I36" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36">
+        <v>7</v>
+      </c>
+      <c r="K36" t="s">
+        <v>78</v>
+      </c>
+      <c r="L36">
+        <v>33</v>
+      </c>
+      <c r="M36" t="s">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>6</v>
+      </c>
+      <c r="O36" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37">
+        <v>70</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>9</v>
+      </c>
+      <c r="H37">
+        <v>61</v>
+      </c>
+      <c r="I37" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>9</v>
+      </c>
+      <c r="L37">
+        <v>34</v>
+      </c>
+      <c r="M37" t="s">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>8</v>
+      </c>
+      <c r="H38">
+        <v>33</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>6</v>
+      </c>
+      <c r="K38" t="s">
+        <v>86</v>
+      </c>
+      <c r="L38">
+        <v>35</v>
+      </c>
+      <c r="M38" t="s">
+        <v>5</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+      <c r="O38" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C39" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D36">
+      <c r="D39">
         <v>22</v>
       </c>
-      <c r="E36" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36">
-        <v>8</v>
-      </c>
-      <c r="H36">
+      <c r="E39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="H39">
         <v>6</v>
       </c>
-      <c r="I36" t="s">
-        <v>1</v>
-      </c>
-      <c r="J36">
+      <c r="I39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39">
         <v>6</v>
       </c>
-      <c r="K36" t="s">
+      <c r="K39" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37">
-        <v>16</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>8</v>
-      </c>
-      <c r="H37">
+      <c r="L39">
+        <v>36</v>
+      </c>
+      <c r="M39" t="s">
+        <v>1</v>
+      </c>
+      <c r="N39">
         <v>7</v>
       </c>
-      <c r="I37" t="s">
-        <v>5</v>
-      </c>
-      <c r="J37">
-        <v>2</v>
-      </c>
-      <c r="K37" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38">
-        <v>15</v>
-      </c>
-      <c r="E38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38">
-        <v>8</v>
-      </c>
-      <c r="H38">
-        <v>8</v>
-      </c>
-      <c r="I38" t="s">
-        <v>5</v>
-      </c>
-      <c r="J38">
-        <v>2</v>
-      </c>
-      <c r="K38" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C39" t="s">
-        <v>63</v>
-      </c>
-      <c r="D39">
-        <v>55</v>
-      </c>
-      <c r="E39" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39">
-        <v>8</v>
-      </c>
-      <c r="H39">
-        <v>11</v>
-      </c>
-      <c r="I39" t="s">
-        <v>1</v>
-      </c>
-      <c r="J39">
-        <v>7</v>
-      </c>
-      <c r="K39" t="s">
-        <v>78</v>
-      </c>
-      <c r="L39">
-        <v>33</v>
-      </c>
-      <c r="M39" t="s">
-        <v>1</v>
-      </c>
-      <c r="N39">
-        <v>6</v>
-      </c>
       <c r="O39" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" t="s">
-        <v>11</v>
+        <v>76</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
         <v>1</v>
@@ -2139,7 +2181,7 @@
         <v>8</v>
       </c>
       <c r="H40">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I40" t="s">
         <v>5</v>
@@ -2148,215 +2190,224 @@
         <v>2</v>
       </c>
       <c r="K40" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>8</v>
+      </c>
+      <c r="H41">
+        <v>8</v>
+      </c>
+      <c r="I41" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42">
+        <v>8</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="H42">
+        <v>12</v>
+      </c>
+      <c r="I42" t="s">
+        <v>5</v>
+      </c>
+      <c r="J42">
+        <v>2</v>
+      </c>
+      <c r="K42" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C41" t="s">
-        <v>47</v>
-      </c>
-      <c r="D41">
-        <v>41</v>
-      </c>
-      <c r="E41" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41">
-        <v>8</v>
-      </c>
-      <c r="H41">
-        <v>19</v>
-      </c>
-      <c r="I41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C42" t="s">
-        <v>65</v>
-      </c>
-      <c r="D42">
-        <v>57</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42">
-        <v>7</v>
-      </c>
-      <c r="H42">
-        <v>21</v>
-      </c>
-      <c r="I42" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42">
-        <v>8</v>
-      </c>
-      <c r="K42" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43">
+        <v>41</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+      <c r="H43">
+        <v>19</v>
+      </c>
+      <c r="I43" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44">
+        <v>57</v>
+      </c>
+      <c r="E44" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>7</v>
+      </c>
+      <c r="H44">
+        <v>21</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>8</v>
+      </c>
+      <c r="K44" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
         <v>44</v>
       </c>
-      <c r="D43">
+      <c r="D45">
         <v>38</v>
       </c>
-      <c r="E43" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43">
-        <v>8</v>
-      </c>
-      <c r="H43">
+      <c r="E45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>8</v>
+      </c>
+      <c r="H45">
         <v>22</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I45" t="s">
         <v>5</v>
-      </c>
-      <c r="J43">
-        <v>2</v>
-      </c>
-      <c r="K43" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44">
-        <v>12</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" s="2">
-        <v>2</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H44" s="2">
-        <v>24</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44">
-        <v>2</v>
-      </c>
-      <c r="K44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D45">
-        <v>13</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="2">
-        <v>2</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H45" s="2">
-        <v>29</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="J45">
         <v>2</v>
       </c>
       <c r="K45" t="s">
+        <v>83</v>
+      </c>
+      <c r="L45">
+        <v>37</v>
+      </c>
+      <c r="M45" t="s">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>5</v>
+      </c>
+      <c r="O45" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46">
+        <v>12</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="2">
+        <v>2</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="2">
+        <v>24</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46">
+        <v>2</v>
+      </c>
+      <c r="K46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47">
+        <v>13</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="2">
+        <v>2</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="2">
+        <v>29</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>2</v>
+      </c>
+      <c r="K47" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C46" t="s">
-        <v>61</v>
-      </c>
-      <c r="D46">
-        <v>53</v>
-      </c>
-      <c r="E46" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46">
-        <v>8</v>
-      </c>
-      <c r="H46">
-        <v>30</v>
-      </c>
-      <c r="I46" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C47" t="s">
-        <v>25</v>
-      </c>
-      <c r="D47">
-        <v>20</v>
-      </c>
-      <c r="E47" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47">
-        <v>8</v>
-      </c>
-      <c r="H47">
-        <v>33</v>
-      </c>
-      <c r="I47" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47">
-        <v>6</v>
-      </c>
-      <c r="K47" t="s">
-        <v>86</v>
-      </c>
-      <c r="L47">
-        <v>35</v>
-      </c>
-      <c r="M47" t="s">
-        <v>5</v>
-      </c>
-      <c r="N47">
-        <v>1</v>
-      </c>
-      <c r="O47" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D48">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E48" t="s">
         <v>1</v>
@@ -2365,21 +2416,21 @@
         <v>8</v>
       </c>
       <c r="H48">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I48" t="s">
         <v>1</v>
       </c>
       <c r="J48">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="D49">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="E49" t="s">
         <v>1</v>
@@ -2388,7 +2439,7 @@
         <v>8</v>
       </c>
       <c r="H49">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I49" t="s">
         <v>1</v>
@@ -2399,10 +2450,10 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D50">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E50" t="s">
         <v>1</v>
@@ -2411,119 +2462,122 @@
         <v>8</v>
       </c>
       <c r="H50">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I50" t="s">
         <v>1</v>
       </c>
       <c r="J50">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51">
+        <v>25</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+      <c r="H51">
+        <v>42</v>
+      </c>
+      <c r="I51" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
         <v>70</v>
       </c>
-      <c r="D51">
+      <c r="D52">
         <v>62</v>
       </c>
-      <c r="E51" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51">
-        <v>8</v>
-      </c>
-      <c r="H51">
+      <c r="E52" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>8</v>
+      </c>
+      <c r="H52">
         <v>43</v>
       </c>
-      <c r="I51" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="I52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D53" s="2">
         <v>4</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F53" s="2">
         <v>2</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G53" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H53" s="2">
         <v>44</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C53" t="s">
-        <v>68</v>
-      </c>
-      <c r="D53">
-        <v>60</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53">
-        <v>2</v>
-      </c>
-      <c r="H53">
-        <v>46</v>
-      </c>
-      <c r="I53" t="s">
-        <v>5</v>
+      <c r="I53" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="J53">
-        <v>2</v>
-      </c>
-      <c r="K53" t="s">
-        <v>87</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D54">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="E54" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F54">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I54" t="s">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J54">
+        <v>2</v>
+      </c>
+      <c r="K54" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D55">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="E55" t="s">
         <v>1</v>
@@ -2532,21 +2586,18 @@
         <v>8</v>
       </c>
       <c r="H55">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I55" t="s">
         <v>1</v>
-      </c>
-      <c r="J55">
-        <v>9</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D56">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E56" t="s">
         <v>1</v>
@@ -2555,7 +2606,7 @@
         <v>8</v>
       </c>
       <c r="H56">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I56" t="s">
         <v>1</v>
@@ -2566,10 +2617,10 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="D57">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="E57" t="s">
         <v>1</v>
@@ -2578,7 +2629,7 @@
         <v>8</v>
       </c>
       <c r="H57">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I57" t="s">
         <v>1</v>
@@ -2589,16 +2640,19 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
-        <v>88</v>
+        <v>9</v>
+      </c>
+      <c r="D58">
+        <v>6</v>
       </c>
       <c r="E58" t="s">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H58">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I58" t="s">
         <v>1</v>
@@ -2609,7 +2663,7 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E59" t="s">
         <v>89</v>
@@ -2618,250 +2672,329 @@
         <v>0</v>
       </c>
       <c r="H59">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I59" t="s">
         <v>1</v>
       </c>
       <c r="J59">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
-        <v>91</v>
+        <v>90</v>
+      </c>
+      <c r="D60">
+        <v>65</v>
       </c>
       <c r="E60" t="s">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H60">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I60" t="s">
         <v>1</v>
       </c>
       <c r="J60">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
+        <v>91</v>
+      </c>
+      <c r="D61">
+        <v>66</v>
+      </c>
+      <c r="E61" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>7</v>
+      </c>
+      <c r="H61">
+        <v>56</v>
+      </c>
+      <c r="I61" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C62" t="s">
+        <v>93</v>
+      </c>
+      <c r="D62">
+        <v>68</v>
+      </c>
+      <c r="E62" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>9</v>
+      </c>
+      <c r="H62">
+        <v>58</v>
+      </c>
+      <c r="I62" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62">
         <v>2</v>
       </c>
-      <c r="D61">
-        <v>2</v>
-      </c>
-      <c r="E61" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D62" s="2">
-        <v>5</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" s="2">
-        <v>2</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H62" s="2"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B63" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D63" s="6">
-        <v>7</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
+      <c r="C63" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63">
+        <v>61</v>
+      </c>
+      <c r="E63" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>8</v>
+      </c>
+      <c r="H63">
+        <v>59</v>
+      </c>
+      <c r="I63" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63">
+        <v>8</v>
+      </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64">
+        <v>2</v>
+      </c>
+      <c r="E64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="2">
+        <v>5</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F65" s="2">
+        <v>2</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H65" s="2"/>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B66" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="6">
+        <v>7</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
         <v>12</v>
       </c>
-      <c r="D64">
+      <c r="D67">
         <v>11</v>
       </c>
-      <c r="E64" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C65" t="s">
+      <c r="E67" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C68" t="s">
         <v>28</v>
       </c>
-      <c r="D65">
+      <c r="D68">
         <v>23</v>
       </c>
-      <c r="E65" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" s="2" t="s">
+      <c r="E68" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>8</v>
+      </c>
+      <c r="H68">
+        <v>63</v>
+      </c>
+      <c r="I68" t="s">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D69" s="2">
         <v>26</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="E69" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F69" s="2">
         <v>2</v>
       </c>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C67" t="s">
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C70" t="s">
         <v>35</v>
       </c>
-      <c r="D67">
+      <c r="D70">
         <v>30</v>
       </c>
-      <c r="E67" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C68" t="s">
+      <c r="E70" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
         <v>41</v>
       </c>
-      <c r="D68">
+      <c r="D71">
         <v>35</v>
       </c>
-      <c r="E68" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B69" s="3" t="s">
+      <c r="E71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>8</v>
+      </c>
+      <c r="H71">
+        <v>60</v>
+      </c>
+      <c r="I71" t="s">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B72" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D72" s="3">
         <v>44</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F72" s="3">
         <v>2</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G72" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C70" t="s">
+      <c r="H72" s="3"/>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
         <v>67</v>
       </c>
-      <c r="D70">
+      <c r="D73">
         <v>59</v>
       </c>
-      <c r="E70" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70">
+      <c r="E73" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73">
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C71" t="s">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C74" t="s">
+        <v>124</v>
+      </c>
+      <c r="D74">
         <v>69</v>
       </c>
-      <c r="D71">
-        <v>61</v>
-      </c>
-      <c r="E71" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71">
-        <v>8</v>
-      </c>
-      <c r="H71">
-        <v>59</v>
-      </c>
-      <c r="I71" t="s">
-        <v>1</v>
-      </c>
-      <c r="J71">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C72" t="s">
-        <v>93</v>
-      </c>
-      <c r="H72">
-        <v>58</v>
-      </c>
-      <c r="I72" t="s">
-        <v>5</v>
-      </c>
-      <c r="J72">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C73" t="s">
-        <v>122</v>
-      </c>
-      <c r="L73">
-        <v>34</v>
-      </c>
-      <c r="M73" t="s">
-        <v>1</v>
-      </c>
-      <c r="N73">
+      <c r="E74" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>6</v>
+      </c>
+      <c r="G74" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C75" t="s">
+        <v>126</v>
+      </c>
+      <c r="D75">
+        <v>71</v>
+      </c>
+      <c r="E75" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75">
+        <v>9</v>
+      </c>
+      <c r="H75">
+        <v>62</v>
+      </c>
+      <c r="I75" t="s">
+        <v>1</v>
+      </c>
+      <c r="J75">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:O72">
-    <sortCondition ref="L4:L72"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:O75">
+    <sortCondition ref="L4:L75"/>
   </sortState>
   <mergeCells count="4">
     <mergeCell ref="B2:C2"/>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E66518C-121B-43A8-9EF4-3A23026B81B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF2C61C-332B-4554-A015-FCE049C1291B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="130">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -415,6 +415,9 @@
   </si>
   <si>
     <t>Falta persistir en localStorage, en varios falta el estado de la aplicación</t>
+  </si>
+  <si>
+    <t>TRABAJO PRÁCTICO NRO. 04</t>
   </si>
 </sst>
 </file>
@@ -446,7 +449,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -501,6 +504,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -514,7 +523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -527,6 +536,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -807,11 +817,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:O75"/>
+  <dimension ref="B2:S75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -821,12 +831,16 @@
     <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="50.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="66.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>16</v>
       </c>
@@ -849,8 +863,14 @@
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P2" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+    </row>
+    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
@@ -893,8 +913,20 @@
       <c r="O3" s="8" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P3" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C4" s="5" t="s">
         <v>54</v>
       </c>
@@ -929,7 +961,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C5" s="5" t="s">
         <v>64</v>
       </c>
@@ -964,7 +996,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>43</v>
       </c>
@@ -998,8 +1030,17 @@
       <c r="O6" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>38</v>
       </c>
@@ -1034,7 +1075,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>12</v>
       </c>
@@ -1069,7 +1110,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>57</v>
       </c>
@@ -1104,7 +1145,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>49</v>
       </c>
@@ -1139,7 +1180,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>48</v>
       </c>
@@ -1174,7 +1215,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>59</v>
       </c>
@@ -1209,7 +1250,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>40</v>
       </c>
@@ -1244,7 +1285,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>56</v>
       </c>
@@ -1279,7 +1320,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C15" s="5" t="s">
         <v>62</v>
       </c>
@@ -1314,7 +1355,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>24</v>
       </c>
@@ -1349,7 +1390,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>60</v>
       </c>
@@ -1386,8 +1427,17 @@
       <c r="O17" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="P17">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>13</v>
       </c>
@@ -1425,7 +1475,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>53</v>
       </c>
@@ -1460,7 +1510,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>23</v>
       </c>
@@ -1495,7 +1545,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>32</v>
       </c>
@@ -1530,7 +1580,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>39</v>
       </c>
@@ -1564,8 +1614,17 @@
       <c r="O22" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="P22">
+        <v>3</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>29</v>
       </c>
@@ -1600,7 +1659,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>55</v>
       </c>
@@ -1635,7 +1694,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>42</v>
       </c>
@@ -1670,7 +1729,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C26" s="5" t="s">
         <v>33</v>
       </c>
@@ -1705,7 +1764,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C27" s="5" t="s">
         <v>26</v>
       </c>
@@ -1740,7 +1799,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>58</v>
       </c>
@@ -1772,7 +1831,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>45</v>
       </c>
@@ -1807,7 +1866,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>46</v>
       </c>
@@ -1842,7 +1901,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>92</v>
       </c>
@@ -1874,7 +1933,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>3</v>
       </c>
@@ -2996,11 +3055,12 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:O75">
     <sortCondition ref="L4:L75"/>
   </sortState>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="H2:K2"/>
     <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF2C61C-332B-4554-A015-FCE049C1291B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81F8EB5-2448-445B-A393-715DACAC559C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$3:$K$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$3:$S$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="133">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -418,6 +418,15 @@
   </si>
   <si>
     <t>TRABAJO PRÁCTICO NRO. 04</t>
+  </si>
+  <si>
+    <t>Correa, Valentín Eliazar</t>
+  </si>
+  <si>
+    <t>Entregó Tarde</t>
+  </si>
+  <si>
+    <t>Utilizo IA</t>
   </si>
 </sst>
 </file>
@@ -533,10 +542,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -817,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:S75"/>
+  <dimension ref="B2:S76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -841,34 +850,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9" t="s">
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9" t="s">
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -913,16 +922,16 @@
       <c r="O3" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="Q3" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="R3" s="10" t="s">
+      <c r="R3" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="S3" s="9" t="s">
         <v>107</v>
       </c>
     </row>
@@ -995,6 +1004,15 @@
       <c r="O5" t="s">
         <v>109</v>
       </c>
+      <c r="P5">
+        <v>7</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
@@ -1074,6 +1092,15 @@
       <c r="O7" t="s">
         <v>110</v>
       </c>
+      <c r="P7">
+        <v>14</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
@@ -1109,6 +1136,15 @@
       <c r="O8" t="s">
         <v>111</v>
       </c>
+      <c r="P8">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
@@ -1144,6 +1180,15 @@
       <c r="O9" t="s">
         <v>112</v>
       </c>
+      <c r="P9">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
@@ -1214,6 +1259,15 @@
       <c r="O11" t="s">
         <v>112</v>
       </c>
+      <c r="P11">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
@@ -1249,6 +1303,12 @@
       <c r="O12" t="s">
         <v>114</v>
       </c>
+      <c r="P12">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
@@ -1319,6 +1379,15 @@
       <c r="O14" t="s">
         <v>114</v>
       </c>
+      <c r="P14">
+        <v>12</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>8</v>
+      </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C15" s="5" t="s">
@@ -1354,6 +1423,12 @@
       <c r="O15" t="s">
         <v>114</v>
       </c>
+      <c r="P15">
+        <v>15</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
@@ -1658,6 +1733,12 @@
       <c r="O23" t="s">
         <v>114</v>
       </c>
+      <c r="P23">
+        <v>6</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
@@ -1965,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>0</v>
       </c>
@@ -2000,7 +2081,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
       <c r="C34" s="5" t="s">
         <v>36</v>
@@ -2041,8 +2122,17 @@
       <c r="O34" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P34">
+        <v>13</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>1</v>
+      </c>
+      <c r="R34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>19</v>
       </c>
@@ -2077,7 +2167,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>63</v>
       </c>
@@ -2115,7 +2205,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
         <v>122</v>
       </c>
@@ -2147,7 +2237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>25</v>
       </c>
@@ -2185,7 +2275,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C39" s="5" t="s">
         <v>27</v>
       </c>
@@ -2223,7 +2313,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>76</v>
       </c>
@@ -2252,7 +2342,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>77</v>
       </c>
@@ -2281,7 +2371,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>80</v>
       </c>
@@ -2310,7 +2400,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>47</v>
       </c>
@@ -2333,7 +2423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>65</v>
       </c>
@@ -2359,7 +2449,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>44</v>
       </c>
@@ -2396,8 +2486,20 @@
       <c r="O45" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P45">
+        <v>11</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R45">
+        <v>4</v>
+      </c>
+      <c r="S45" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
         <v>31</v>
       </c>
@@ -2429,7 +2531,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
         <v>31</v>
       </c>
@@ -2461,7 +2563,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>61</v>
       </c>
@@ -2484,7 +2586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>34</v>
       </c>
@@ -2507,7 +2609,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>71</v>
       </c>
@@ -2530,7 +2632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
         <v>30</v>
       </c>
@@ -2553,7 +2655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C52" t="s">
         <v>70</v>
       </c>
@@ -2576,7 +2678,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
         <v>8</v>
       </c>
@@ -2605,7 +2707,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
         <v>68</v>
       </c>
@@ -2631,7 +2733,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>22</v>
       </c>
@@ -2650,8 +2752,20 @@
       <c r="I55" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L55">
+        <v>38</v>
+      </c>
+      <c r="M55" t="s">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <v>10</v>
+      </c>
+      <c r="O55" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
         <v>66</v>
       </c>
@@ -2674,7 +2788,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
         <v>72</v>
       </c>
@@ -2697,7 +2811,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
         <v>9</v>
       </c>
@@ -2720,7 +2834,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
         <v>88</v>
       </c>
@@ -2740,7 +2854,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
         <v>90</v>
       </c>
@@ -2763,7 +2877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
         <v>91</v>
       </c>
@@ -2786,7 +2900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
         <v>93</v>
       </c>
@@ -2809,7 +2923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
         <v>69</v>
       </c>
@@ -2832,7 +2946,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
         <v>2</v>
       </c>
@@ -2846,7 +2960,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
         <v>8</v>
       </c>
@@ -2867,7 +2981,7 @@
       </c>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" s="6" t="s">
         <v>8</v>
       </c>
@@ -2883,7 +2997,7 @@
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>12</v>
       </c>
@@ -2897,7 +3011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
         <v>28</v>
       </c>
@@ -2920,7 +3034,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
         <v>8</v>
       </c>
@@ -2939,7 +3053,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>35</v>
       </c>
@@ -2953,7 +3067,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
         <v>41</v>
       </c>
@@ -2976,7 +3090,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
         <v>51</v>
       </c>
@@ -2997,7 +3111,7 @@
       </c>
       <c r="H72" s="3"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C73" t="s">
         <v>67</v>
       </c>
@@ -3011,7 +3125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C74" t="s">
         <v>124</v>
       </c>
@@ -3028,7 +3142,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C75" t="s">
         <v>126</v>
       </c>
@@ -3051,7 +3165,37 @@
         <v>8</v>
       </c>
     </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>130</v>
+      </c>
+      <c r="D76">
+        <v>72</v>
+      </c>
+      <c r="E76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>9</v>
+      </c>
+      <c r="G76" t="s">
+        <v>131</v>
+      </c>
+      <c r="H76">
+        <v>64</v>
+      </c>
+      <c r="I76" t="s">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>8</v>
+      </c>
+      <c r="K76" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="B3:S3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:O75">
     <sortCondition ref="L4:L75"/>
   </sortState>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81F8EB5-2448-445B-A393-715DACAC559C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE9F83C-8698-44D7-A34F-6E4287488477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="138">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -427,6 +427,21 @@
   </si>
   <si>
     <t>Utilizo IA</t>
+  </si>
+  <si>
+    <t>ORDEN 4</t>
+  </si>
+  <si>
+    <t>RESULTADO 4</t>
+  </si>
+  <si>
+    <t>NOTA 4</t>
+  </si>
+  <si>
+    <t>OBSERVACIONES 4</t>
+  </si>
+  <si>
+    <t>Flores, Ana Paula</t>
   </si>
 </sst>
 </file>
@@ -826,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:S76"/>
+  <dimension ref="B2:S77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -923,24 +938,24 @@
         <v>107</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C4" s="5" t="s">
-        <v>54</v>
+      <c r="C4" t="s">
+        <v>43</v>
       </c>
       <c r="D4">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>1</v>
@@ -949,16 +964,16 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="I4" t="s">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" t="s">
         <v>1</v>
@@ -969,13 +984,22 @@
       <c r="O4" t="s">
         <v>109</v>
       </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C5" s="5" t="s">
-        <v>64</v>
+      <c r="C5" t="s">
+        <v>60</v>
       </c>
       <c r="D5">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>1</v>
@@ -984,42 +1008,45 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I5" t="s">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K5" t="s">
+        <v>78</v>
       </c>
       <c r="L5">
+        <v>14</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>9</v>
+      </c>
+      <c r="O5" t="s">
+        <v>114</v>
+      </c>
+      <c r="P5">
         <v>2</v>
       </c>
-      <c r="M5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>9</v>
-      </c>
-      <c r="O5" t="s">
-        <v>109</v>
-      </c>
-      <c r="P5">
-        <v>7</v>
-      </c>
       <c r="Q5" t="s">
         <v>1</v>
       </c>
       <c r="R5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
         <v>1</v>
@@ -1028,28 +1055,28 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
         <v>1</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>9</v>
+      </c>
+      <c r="O6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P6">
         <v>3</v>
-      </c>
-      <c r="M6" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>9</v>
-      </c>
-      <c r="O6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
       </c>
       <c r="Q6" t="s">
         <v>1</v>
@@ -1060,54 +1087,51 @@
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
         <v>1</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7">
+        <v>9</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>9</v>
+      </c>
+      <c r="O7" t="s">
+        <v>114</v>
+      </c>
+      <c r="P7">
         <v>4</v>
       </c>
-      <c r="M7" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>9</v>
-      </c>
-      <c r="O7" t="s">
-        <v>110</v>
-      </c>
-      <c r="P7">
-        <v>14</v>
-      </c>
       <c r="Q7" t="s">
         <v>1</v>
-      </c>
-      <c r="R7">
-        <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
         <v>1</v>
@@ -1116,28 +1140,28 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
         <v>1</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L8">
+        <v>6</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>10</v>
+      </c>
+      <c r="O8" t="s">
+        <v>112</v>
+      </c>
+      <c r="P8">
         <v>5</v>
-      </c>
-      <c r="M8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>9</v>
-      </c>
-      <c r="O8" t="s">
-        <v>111</v>
-      </c>
-      <c r="P8">
-        <v>8</v>
       </c>
       <c r="Q8" t="s">
         <v>1</v>
@@ -1148,10 +1172,10 @@
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="D9">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
         <v>1</v>
@@ -1160,77 +1184,83 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s">
         <v>1</v>
       </c>
       <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="L9">
+        <v>20</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>9</v>
+      </c>
+      <c r="O9" t="s">
+        <v>114</v>
+      </c>
+      <c r="P9">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C10" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>9</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>9</v>
+      </c>
+      <c r="O10" t="s">
+        <v>109</v>
+      </c>
+      <c r="P10">
         <v>7</v>
       </c>
-      <c r="L9">
-        <v>6</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>10</v>
-      </c>
-      <c r="O9" t="s">
-        <v>112</v>
-      </c>
-      <c r="P9">
-        <v>5</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>8</v>
-      </c>
-      <c r="H10">
-        <v>20</v>
-      </c>
-      <c r="I10" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>7</v>
-      </c>
-      <c r="L10">
-        <v>7</v>
-      </c>
-      <c r="M10" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <v>5</v>
-      </c>
-      <c r="O10" t="s">
-        <v>113</v>
+      <c r="Q10" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="D11">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
         <v>1</v>
@@ -1239,28 +1269,28 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
         <v>1</v>
       </c>
       <c r="J11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M11" t="s">
         <v>1</v>
       </c>
       <c r="N11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="s">
         <v>1</v>
@@ -1271,51 +1301,54 @@
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D12">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H12">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I12" t="s">
         <v>1</v>
       </c>
       <c r="J12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M12" t="s">
         <v>1</v>
       </c>
       <c r="N12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P12">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="s">
         <v>1</v>
+      </c>
+      <c r="R12">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D13">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>1</v>
@@ -1324,25 +1357,40 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>83</v>
       </c>
       <c r="L13">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="M13" t="s">
         <v>1</v>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O13" t="s">
-        <v>115</v>
+        <v>128</v>
+      </c>
+      <c r="P13">
+        <v>11</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>4</v>
+      </c>
+      <c r="S13" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
@@ -1390,52 +1438,62 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B15" s="3"/>
       <c r="C15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15">
-        <v>54</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>8</v>
-      </c>
-      <c r="H15">
+        <v>36</v>
+      </c>
+      <c r="D15" s="3">
+        <v>31</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3">
         <v>2</v>
       </c>
-      <c r="I15" t="s">
+      <c r="G15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>1</v>
       </c>
       <c r="J15">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="L15">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="M15" t="s">
         <v>1</v>
       </c>
       <c r="N15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q15" t="s">
         <v>1</v>
+      </c>
+      <c r="R15">
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D16">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
         <v>1</v>
@@ -1444,66 +1502,72 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I16" t="s">
         <v>1</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M16" t="s">
         <v>1</v>
       </c>
       <c r="N16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
-        <v>60</v>
+        <v>110</v>
+      </c>
+      <c r="P16">
+        <v>14</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C17" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="D17">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E17" t="s">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H17">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I17" t="s">
         <v>1</v>
       </c>
       <c r="J17">
-        <v>7</v>
-      </c>
-      <c r="K17" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M17" t="s">
         <v>1</v>
       </c>
       <c r="N17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O17" t="s">
         <v>114</v>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Q17" t="s">
         <v>1</v>
@@ -1512,185 +1576,182 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="D18">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>9</v>
+      </c>
+      <c r="H18">
+        <v>61</v>
+      </c>
+      <c r="I18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>9</v>
+      </c>
+      <c r="L18">
+        <v>34</v>
+      </c>
+      <c r="M18" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>8</v>
+      </c>
+      <c r="P18">
+        <v>16</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19">
+        <v>47</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>8</v>
+      </c>
+      <c r="H19">
         <v>10</v>
       </c>
-      <c r="E18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>8</v>
-      </c>
-      <c r="H18">
-        <v>14</v>
-      </c>
-      <c r="I18" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18">
+      <c r="I19" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19">
         <v>7</v>
       </c>
-      <c r="K18" t="s">
-        <v>81</v>
-      </c>
-      <c r="L18">
+      <c r="L19">
+        <v>21</v>
+      </c>
+      <c r="M19" t="s">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>9</v>
+      </c>
+      <c r="O19" t="s">
+        <v>114</v>
+      </c>
+      <c r="P19">
+        <v>17</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20">
+        <v>50</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>8</v>
+      </c>
+      <c r="H20">
+        <v>32</v>
+      </c>
+      <c r="I20" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>9</v>
+      </c>
+      <c r="L20">
+        <v>25</v>
+      </c>
+      <c r="M20" t="s">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>9</v>
+      </c>
+      <c r="P20">
+        <v>18</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+      <c r="P21">
+        <v>19</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22">
+        <v>45</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="H22">
         <v>15</v>
       </c>
-      <c r="M18" t="s">
-        <v>1</v>
-      </c>
-      <c r="N18">
-        <v>8</v>
-      </c>
-      <c r="O18" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19">
-        <v>45</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19">
+      <c r="I22" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22">
         <v>10</v>
       </c>
-      <c r="H19">
-        <v>15</v>
-      </c>
-      <c r="I19" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19">
+      <c r="K22" t="s">
+        <v>82</v>
+      </c>
+      <c r="L22">
+        <v>16</v>
+      </c>
+      <c r="M22" t="s">
+        <v>1</v>
+      </c>
+      <c r="N22">
         <v>10</v>
       </c>
-      <c r="K19" t="s">
-        <v>82</v>
-      </c>
-      <c r="L19">
-        <v>16</v>
-      </c>
-      <c r="M19" t="s">
-        <v>1</v>
-      </c>
-      <c r="N19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20">
-        <v>8</v>
-      </c>
-      <c r="H20">
-        <v>36</v>
-      </c>
-      <c r="I20" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>9</v>
-      </c>
-      <c r="L20">
-        <v>17</v>
-      </c>
-      <c r="M20" t="s">
-        <v>1</v>
-      </c>
-      <c r="N20">
-        <v>7</v>
-      </c>
-      <c r="O20" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21">
-        <v>27</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21">
-        <v>8</v>
-      </c>
-      <c r="H21">
-        <v>16</v>
-      </c>
-      <c r="I21" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <v>7</v>
-      </c>
-      <c r="L21">
-        <v>18</v>
-      </c>
-      <c r="M21" t="s">
-        <v>1</v>
-      </c>
-      <c r="N21">
-        <v>9</v>
-      </c>
-      <c r="O21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22">
-        <v>33</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>8</v>
-      </c>
-      <c r="H22">
-        <v>18</v>
-      </c>
-      <c r="I22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>5</v>
-      </c>
-      <c r="L22">
-        <v>19</v>
-      </c>
-      <c r="M22" t="s">
-        <v>1</v>
-      </c>
-      <c r="N22">
-        <v>9</v>
-      </c>
-      <c r="O22" t="s">
-        <v>114</v>
-      </c>
       <c r="P22">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Q22" t="s">
         <v>1</v>
@@ -1698,13 +1759,16 @@
       <c r="R22">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>29</v>
+      <c r="S22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C23" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="D23">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E23" t="s">
         <v>1</v>
@@ -1713,48 +1777,42 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I23" t="s">
         <v>1</v>
       </c>
       <c r="J23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23" t="s">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>9</v>
+      </c>
+      <c r="O23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24">
+        <v>43</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>8</v>
+      </c>
+      <c r="H24">
         <v>20</v>
-      </c>
-      <c r="M23" t="s">
-        <v>1</v>
-      </c>
-      <c r="N23">
-        <v>9</v>
-      </c>
-      <c r="O23" t="s">
-        <v>114</v>
-      </c>
-      <c r="P23">
-        <v>6</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24">
-        <v>47</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>8</v>
-      </c>
-      <c r="H24">
-        <v>10</v>
       </c>
       <c r="I24" t="s">
         <v>1</v>
@@ -1763,425 +1821,445 @@
         <v>7</v>
       </c>
       <c r="L24">
+        <v>7</v>
+      </c>
+      <c r="M24" t="s">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>5</v>
+      </c>
+      <c r="O24" t="s">
+        <v>113</v>
+      </c>
+      <c r="P24">
+        <v>22</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>8</v>
+      </c>
+      <c r="H25">
+        <v>25</v>
+      </c>
+      <c r="I25" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>10</v>
+      </c>
+      <c r="L25">
+        <v>10</v>
+      </c>
+      <c r="M25" t="s">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>7</v>
+      </c>
+      <c r="O25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26">
+        <v>19</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="H26">
+        <v>27</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>7</v>
+      </c>
+      <c r="L26">
+        <v>13</v>
+      </c>
+      <c r="M26" t="s">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>7</v>
+      </c>
+      <c r="O26" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>8</v>
+      </c>
+      <c r="H27">
+        <v>14</v>
+      </c>
+      <c r="I27" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>7</v>
+      </c>
+      <c r="K27" t="s">
+        <v>81</v>
+      </c>
+      <c r="L27">
+        <v>15</v>
+      </c>
+      <c r="M27" t="s">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>8</v>
+      </c>
+      <c r="O27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>8</v>
+      </c>
+      <c r="H28">
+        <v>36</v>
+      </c>
+      <c r="I28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>9</v>
+      </c>
+      <c r="L28">
+        <v>17</v>
+      </c>
+      <c r="M28" t="s">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>7</v>
+      </c>
+      <c r="O28" t="s">
+        <v>117</v>
+      </c>
+      <c r="P28">
+        <v>24</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>1</v>
+      </c>
+      <c r="R28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29">
+        <v>27</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>8</v>
+      </c>
+      <c r="H29">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>7</v>
+      </c>
+      <c r="L29">
+        <v>18</v>
+      </c>
+      <c r="M29" t="s">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>9</v>
+      </c>
+      <c r="O29" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30">
+        <v>36</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
+      </c>
+      <c r="H30">
+        <v>38</v>
+      </c>
+      <c r="I30" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>9</v>
+      </c>
+      <c r="L30">
+        <v>22</v>
+      </c>
+      <c r="M30" t="s">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>9</v>
+      </c>
+      <c r="O30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31">
+        <v>28</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>8</v>
+      </c>
+      <c r="H31">
+        <v>5</v>
+      </c>
+      <c r="I31" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>8</v>
+      </c>
+      <c r="L31">
+        <v>23</v>
+      </c>
+      <c r="M31" t="s">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>9</v>
+      </c>
+      <c r="O31" t="s">
+        <v>114</v>
+      </c>
+      <c r="P31">
         <v>21</v>
       </c>
-      <c r="M24" t="s">
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <v>9</v>
-      </c>
-      <c r="O24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
-        <v>42</v>
-      </c>
-      <c r="D25">
-        <v>36</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>8</v>
-      </c>
-      <c r="H25">
-        <v>38</v>
-      </c>
-      <c r="I25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>9</v>
-      </c>
-      <c r="L25">
-        <v>22</v>
-      </c>
-      <c r="M25" t="s">
-        <v>1</v>
-      </c>
-      <c r="N25">
-        <v>9</v>
-      </c>
-      <c r="O25" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26">
+      <c r="Q31" t="s">
+        <v>1</v>
+      </c>
+      <c r="R31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C32" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32">
+        <v>21</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>8</v>
+      </c>
+      <c r="H32">
+        <v>9</v>
+      </c>
+      <c r="I32" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>6</v>
+      </c>
+      <c r="L32">
+        <v>24</v>
+      </c>
+      <c r="M32" t="s">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>8</v>
+      </c>
+      <c r="O32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33">
+        <v>39</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+      <c r="H33">
+        <v>26</v>
+      </c>
+      <c r="I33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>8</v>
+      </c>
+      <c r="L33">
+        <v>26</v>
+      </c>
+      <c r="M33" t="s">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>9</v>
+      </c>
+      <c r="O33" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34">
+        <v>40</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>8</v>
+      </c>
+      <c r="H34">
+        <v>34</v>
+      </c>
+      <c r="I34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>9</v>
+      </c>
+      <c r="L34">
+        <v>27</v>
+      </c>
+      <c r="M34" t="s">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>8</v>
+      </c>
+      <c r="O34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35">
+        <v>67</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>9</v>
+      </c>
+      <c r="H35">
+        <v>57</v>
+      </c>
+      <c r="I35" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>7</v>
+      </c>
+      <c r="L35">
         <v>28</v>
       </c>
-      <c r="E26" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>8</v>
-      </c>
-      <c r="H26">
-        <v>5</v>
-      </c>
-      <c r="I26" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>8</v>
-      </c>
-      <c r="L26">
-        <v>23</v>
-      </c>
-      <c r="M26" t="s">
-        <v>1</v>
-      </c>
-      <c r="N26">
-        <v>9</v>
-      </c>
-      <c r="O26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C27" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27">
-        <v>21</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>8</v>
-      </c>
-      <c r="H27">
-        <v>9</v>
-      </c>
-      <c r="I27" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27">
-        <v>6</v>
-      </c>
-      <c r="L27">
-        <v>24</v>
-      </c>
-      <c r="M27" t="s">
-        <v>1</v>
-      </c>
-      <c r="N27">
-        <v>8</v>
-      </c>
-      <c r="O27" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C28" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28">
-        <v>50</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <v>8</v>
-      </c>
-      <c r="H28">
-        <v>32</v>
-      </c>
-      <c r="I28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28">
-        <v>9</v>
-      </c>
-      <c r="L28">
-        <v>25</v>
-      </c>
-      <c r="M28" t="s">
-        <v>1</v>
-      </c>
-      <c r="N28">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29">
-        <v>39</v>
-      </c>
-      <c r="E29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>8</v>
-      </c>
-      <c r="H29">
-        <v>26</v>
-      </c>
-      <c r="I29" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29">
-        <v>8</v>
-      </c>
-      <c r="L29">
-        <v>26</v>
-      </c>
-      <c r="M29" t="s">
-        <v>1</v>
-      </c>
-      <c r="N29">
-        <v>9</v>
-      </c>
-      <c r="O29" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30">
-        <v>40</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <v>8</v>
-      </c>
-      <c r="H30">
-        <v>34</v>
-      </c>
-      <c r="I30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J30">
-        <v>9</v>
-      </c>
-      <c r="L30">
-        <v>27</v>
-      </c>
-      <c r="M30" t="s">
-        <v>1</v>
-      </c>
-      <c r="N30">
-        <v>8</v>
-      </c>
-      <c r="O30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C31" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31">
-        <v>67</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <v>9</v>
-      </c>
-      <c r="H31">
-        <v>57</v>
-      </c>
-      <c r="I31" t="s">
-        <v>1</v>
-      </c>
-      <c r="J31">
-        <v>7</v>
-      </c>
-      <c r="L31">
-        <v>28</v>
-      </c>
-      <c r="M31" t="s">
-        <v>1</v>
-      </c>
-      <c r="N31">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C32" t="s">
+      <c r="M35" t="s">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
         <v>3</v>
       </c>
-      <c r="D32">
+      <c r="D36">
         <v>3</v>
       </c>
-      <c r="E32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32">
-        <v>8</v>
-      </c>
-      <c r="H32">
+      <c r="E36" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>8</v>
+      </c>
+      <c r="H36">
         <v>47</v>
-      </c>
-      <c r="I32" t="s">
-        <v>1</v>
-      </c>
-      <c r="J32">
-        <v>7</v>
-      </c>
-      <c r="L32">
-        <v>29</v>
-      </c>
-      <c r="M32" t="s">
-        <v>1</v>
-      </c>
-      <c r="N32">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C33" t="s">
-        <v>0</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33">
-        <v>8</v>
-      </c>
-      <c r="H33">
-        <v>48</v>
-      </c>
-      <c r="I33" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33">
-        <v>8</v>
-      </c>
-      <c r="L33">
-        <v>30</v>
-      </c>
-      <c r="M33" t="s">
-        <v>1</v>
-      </c>
-      <c r="N33">
-        <v>9</v>
-      </c>
-      <c r="O33" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B34" s="3"/>
-      <c r="C34" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="3">
-        <v>31</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" s="3">
-        <v>2</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H34" s="3">
-        <v>1</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34">
-        <v>7</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="L34">
-        <v>31</v>
-      </c>
-      <c r="M34" t="s">
-        <v>1</v>
-      </c>
-      <c r="N34">
-        <v>9</v>
-      </c>
-      <c r="O34" t="s">
-        <v>112</v>
-      </c>
-      <c r="P34">
-        <v>13</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>1</v>
-      </c>
-      <c r="R34">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35">
-        <v>14</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35">
-        <v>8</v>
-      </c>
-      <c r="H35">
-        <v>49</v>
-      </c>
-      <c r="I35" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35">
-        <v>9</v>
-      </c>
-      <c r="L35">
-        <v>32</v>
-      </c>
-      <c r="M35" t="s">
-        <v>1</v>
-      </c>
-      <c r="N35">
-        <v>9</v>
-      </c>
-      <c r="O35" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C36" t="s">
-        <v>63</v>
-      </c>
-      <c r="D36">
-        <v>55</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36">
-        <v>8</v>
-      </c>
-      <c r="H36">
-        <v>11</v>
       </c>
       <c r="I36" t="s">
         <v>1</v>
@@ -2189,206 +2267,227 @@
       <c r="J36">
         <v>7</v>
       </c>
-      <c r="K36" t="s">
+      <c r="L36">
+        <v>29</v>
+      </c>
+      <c r="M36" t="s">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>8</v>
+      </c>
+      <c r="H37">
+        <v>48</v>
+      </c>
+      <c r="I37" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>8</v>
+      </c>
+      <c r="L37">
+        <v>30</v>
+      </c>
+      <c r="M37" t="s">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>9</v>
+      </c>
+      <c r="O37" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>8</v>
+      </c>
+      <c r="H38">
+        <v>49</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>9</v>
+      </c>
+      <c r="L38">
+        <v>32</v>
+      </c>
+      <c r="M38" t="s">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>9</v>
+      </c>
+      <c r="O38" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39">
+        <v>55</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="H39">
+        <v>11</v>
+      </c>
+      <c r="I39" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>7</v>
+      </c>
+      <c r="K39" t="s">
         <v>78</v>
       </c>
-      <c r="L36">
+      <c r="L39">
         <v>33</v>
       </c>
-      <c r="M36" t="s">
-        <v>1</v>
-      </c>
-      <c r="N36">
+      <c r="M39" t="s">
+        <v>1</v>
+      </c>
+      <c r="N39">
         <v>6</v>
       </c>
-      <c r="O36" t="s">
+      <c r="O39" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C37" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37">
-        <v>70</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>9</v>
-      </c>
-      <c r="H37">
-        <v>61</v>
-      </c>
-      <c r="I37" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37">
-        <v>9</v>
-      </c>
-      <c r="L37">
-        <v>34</v>
-      </c>
-      <c r="M37" t="s">
-        <v>1</v>
-      </c>
-      <c r="N37">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C38" t="s">
+      <c r="P39">
+        <v>23</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>1</v>
+      </c>
+      <c r="R39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
         <v>25</v>
       </c>
-      <c r="D38">
+      <c r="D40">
         <v>20</v>
       </c>
-      <c r="E38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38">
-        <v>8</v>
-      </c>
-      <c r="H38">
+      <c r="E40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>8</v>
+      </c>
+      <c r="H40">
         <v>33</v>
       </c>
-      <c r="I38" t="s">
-        <v>1</v>
-      </c>
-      <c r="J38">
+      <c r="I40" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40">
         <v>6</v>
       </c>
-      <c r="K38" t="s">
+      <c r="K40" t="s">
         <v>86</v>
       </c>
-      <c r="L38">
+      <c r="L40">
         <v>35</v>
       </c>
-      <c r="M38" t="s">
+      <c r="M40" t="s">
         <v>5</v>
       </c>
-      <c r="N38">
-        <v>1</v>
-      </c>
-      <c r="O38" t="s">
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="O40" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C39" s="5" t="s">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C41" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D39">
+      <c r="D41">
         <v>22</v>
       </c>
-      <c r="E39" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39">
-        <v>8</v>
-      </c>
-      <c r="H39">
+      <c r="E41" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>8</v>
+      </c>
+      <c r="H41">
         <v>6</v>
       </c>
-      <c r="I39" t="s">
-        <v>1</v>
-      </c>
-      <c r="J39">
+      <c r="I41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41">
         <v>6</v>
       </c>
-      <c r="K39" t="s">
+      <c r="K41" t="s">
         <v>74</v>
       </c>
-      <c r="L39">
+      <c r="L41">
         <v>36</v>
       </c>
-      <c r="M39" t="s">
-        <v>1</v>
-      </c>
-      <c r="N39">
+      <c r="M41" t="s">
+        <v>1</v>
+      </c>
+      <c r="N41">
         <v>7</v>
       </c>
-      <c r="O39" t="s">
+      <c r="O41" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D40">
+      <c r="D42">
         <v>16</v>
       </c>
-      <c r="E40" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40">
-        <v>8</v>
-      </c>
-      <c r="H40">
+      <c r="E42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="H42">
         <v>7</v>
-      </c>
-      <c r="I40" t="s">
-        <v>5</v>
-      </c>
-      <c r="J40">
-        <v>2</v>
-      </c>
-      <c r="K40" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B41" t="s">
-        <v>77</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41">
-        <v>15</v>
-      </c>
-      <c r="E41" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41">
-        <v>8</v>
-      </c>
-      <c r="H41">
-        <v>8</v>
-      </c>
-      <c r="I41" t="s">
-        <v>5</v>
-      </c>
-      <c r="J41">
-        <v>2</v>
-      </c>
-      <c r="K41" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42">
-        <v>8</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42">
-        <v>8</v>
-      </c>
-      <c r="H42">
-        <v>12</v>
       </c>
       <c r="I42" t="s">
         <v>5</v>
@@ -2397,149 +2496,125 @@
         <v>2</v>
       </c>
       <c r="K42" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43">
+        <v>15</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+      <c r="H43">
+        <v>8</v>
+      </c>
+      <c r="I43" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44">
+        <v>8</v>
+      </c>
+      <c r="E44" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>8</v>
+      </c>
+      <c r="H44">
+        <v>12</v>
+      </c>
+      <c r="I44" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C43" t="s">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
         <v>47</v>
       </c>
-      <c r="D43">
+      <c r="D45">
         <v>41</v>
       </c>
-      <c r="E43" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43">
-        <v>8</v>
-      </c>
-      <c r="H43">
+      <c r="E45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>8</v>
+      </c>
+      <c r="H45">
         <v>19</v>
       </c>
-      <c r="I43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43">
+      <c r="I45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45">
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C44" t="s">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
         <v>65</v>
       </c>
-      <c r="D44">
+      <c r="D46">
         <v>57</v>
       </c>
-      <c r="E44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44">
+      <c r="E46" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46">
         <v>7</v>
       </c>
-      <c r="H44">
+      <c r="H46">
         <v>21</v>
       </c>
-      <c r="I44" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44">
-        <v>8</v>
-      </c>
-      <c r="K44" t="s">
+      <c r="I46" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>8</v>
+      </c>
+      <c r="K46" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C45" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45">
-        <v>38</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45">
-        <v>8</v>
-      </c>
-      <c r="H45">
-        <v>22</v>
-      </c>
-      <c r="I45" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45">
-        <v>2</v>
-      </c>
-      <c r="K45" t="s">
-        <v>83</v>
-      </c>
-      <c r="L45">
-        <v>37</v>
-      </c>
-      <c r="M45" t="s">
-        <v>1</v>
-      </c>
-      <c r="N45">
-        <v>5</v>
-      </c>
-      <c r="O45" t="s">
-        <v>128</v>
-      </c>
-      <c r="P45">
-        <v>11</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>1</v>
-      </c>
-      <c r="R45">
-        <v>4</v>
-      </c>
-      <c r="S45" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46">
-        <v>12</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" s="2">
-        <v>2</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H46" s="2">
-        <v>24</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J46">
-        <v>2</v>
-      </c>
-      <c r="K46" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D47">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>5</v>
@@ -2551,47 +2626,56 @@
         <v>18</v>
       </c>
       <c r="H47" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J47">
         <v>2</v>
       </c>
       <c r="K47" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48">
+        <v>13</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="2">
+        <v>2</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="2">
+        <v>29</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="K48" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C48" t="s">
-        <v>61</v>
-      </c>
-      <c r="D48">
-        <v>53</v>
-      </c>
-      <c r="E48" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48">
-        <v>8</v>
-      </c>
-      <c r="H48">
-        <v>30</v>
-      </c>
-      <c r="I48" t="s">
-        <v>1</v>
-      </c>
-      <c r="J48">
-        <v>5</v>
       </c>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D49">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E49" t="s">
         <v>1</v>
@@ -2600,21 +2684,21 @@
         <v>8</v>
       </c>
       <c r="H49">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I49" t="s">
         <v>1</v>
       </c>
       <c r="J49">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="D50">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="E50" t="s">
         <v>1</v>
@@ -2623,7 +2707,7 @@
         <v>8</v>
       </c>
       <c r="H50">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I50" t="s">
         <v>1</v>
@@ -2634,10 +2718,10 @@
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D51">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E51" t="s">
         <v>1</v>
@@ -2646,131 +2730,122 @@
         <v>8</v>
       </c>
       <c r="H51">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I51" t="s">
         <v>1</v>
       </c>
       <c r="J51">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C52" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52">
+        <v>25</v>
+      </c>
+      <c r="E52" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>8</v>
+      </c>
+      <c r="H52">
+        <v>42</v>
+      </c>
+      <c r="I52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
         <v>70</v>
       </c>
-      <c r="D52">
+      <c r="D53">
         <v>62</v>
       </c>
-      <c r="E52" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52">
-        <v>8</v>
-      </c>
-      <c r="H52">
+      <c r="E53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>8</v>
+      </c>
+      <c r="H53">
         <v>43</v>
       </c>
-      <c r="I52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="I53" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D54" s="2">
         <v>4</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F54" s="2">
         <v>2</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G54" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H54" s="2">
         <v>44</v>
       </c>
-      <c r="I53" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C54" t="s">
-        <v>68</v>
-      </c>
-      <c r="D54">
-        <v>60</v>
-      </c>
-      <c r="E54" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54">
-        <v>2</v>
-      </c>
-      <c r="H54">
-        <v>46</v>
-      </c>
-      <c r="I54" t="s">
-        <v>5</v>
+      <c r="I54" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="J54">
-        <v>2</v>
-      </c>
-      <c r="K54" t="s">
-        <v>87</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D55">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="E55" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F55">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H55">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>1</v>
-      </c>
-      <c r="L55">
-        <v>38</v>
-      </c>
-      <c r="M55" t="s">
-        <v>1</v>
-      </c>
-      <c r="N55">
-        <v>10</v>
-      </c>
-      <c r="O55" t="s">
-        <v>112</v>
+        <v>5</v>
+      </c>
+      <c r="J55">
+        <v>2</v>
+      </c>
+      <c r="K55" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D56">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="E56" t="s">
         <v>1</v>
@@ -2779,21 +2854,30 @@
         <v>8</v>
       </c>
       <c r="H56">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I56" t="s">
         <v>1</v>
       </c>
-      <c r="J56">
-        <v>9</v>
+      <c r="L56">
+        <v>38</v>
+      </c>
+      <c r="M56" t="s">
+        <v>1</v>
+      </c>
+      <c r="N56">
+        <v>10</v>
+      </c>
+      <c r="O56" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D57">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E57" t="s">
         <v>1</v>
@@ -2802,7 +2886,7 @@
         <v>8</v>
       </c>
       <c r="H57">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I57" t="s">
         <v>1</v>
@@ -2813,10 +2897,10 @@
     </row>
     <row r="58" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="D58">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="E58" t="s">
         <v>1</v>
@@ -2825,7 +2909,7 @@
         <v>8</v>
       </c>
       <c r="H58">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I58" t="s">
         <v>1</v>
@@ -2836,16 +2920,19 @@
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
-        <v>88</v>
+        <v>9</v>
+      </c>
+      <c r="D59">
+        <v>6</v>
       </c>
       <c r="E59" t="s">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H59">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I59" t="s">
         <v>1</v>
@@ -2856,348 +2943,368 @@
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
-        <v>90</v>
-      </c>
-      <c r="D60">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="E60" t="s">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="F60">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I60" t="s">
         <v>1</v>
       </c>
       <c r="J60">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D61">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E61" t="s">
         <v>1</v>
       </c>
       <c r="F61">
+        <v>8</v>
+      </c>
+      <c r="H61">
+        <v>55</v>
+      </c>
+      <c r="I61" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61">
         <v>7</v>
-      </c>
-      <c r="H61">
-        <v>56</v>
-      </c>
-      <c r="I61" t="s">
-        <v>1</v>
-      </c>
-      <c r="J61">
-        <v>9</v>
       </c>
     </row>
     <row r="62" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D62">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E62" t="s">
         <v>1</v>
       </c>
       <c r="F62">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H62">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I62" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J62">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="D63">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E63" t="s">
         <v>1</v>
       </c>
       <c r="F63">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H63">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I63" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J63">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
+        <v>69</v>
+      </c>
+      <c r="D64">
+        <v>61</v>
+      </c>
+      <c r="E64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>8</v>
+      </c>
+      <c r="H64">
+        <v>59</v>
+      </c>
+      <c r="I64" t="s">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C65" t="s">
         <v>2</v>
       </c>
-      <c r="D64">
+      <c r="D65">
         <v>2</v>
       </c>
-      <c r="E64" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C65" s="2" t="s">
+      <c r="E65" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D66" s="2">
         <v>5</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F66" s="2">
         <v>2</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G66" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="2"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B66" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" s="6" t="s">
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B67" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D67" s="6">
         <v>7</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="E67" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C67" t="s">
-        <v>12</v>
-      </c>
-      <c r="D67">
-        <v>11</v>
-      </c>
-      <c r="E67" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67">
-        <v>8</v>
-      </c>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C69" t="s">
         <v>28</v>
       </c>
-      <c r="D68">
+      <c r="D69">
         <v>23</v>
       </c>
-      <c r="E68" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68">
-        <v>8</v>
-      </c>
-      <c r="H68">
+      <c r="E69" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69">
+        <v>8</v>
+      </c>
+      <c r="H69">
         <v>63</v>
       </c>
-      <c r="I68" t="s">
-        <v>1</v>
-      </c>
-      <c r="J68">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C69" s="2" t="s">
+      <c r="I69" t="s">
+        <v>1</v>
+      </c>
+      <c r="J69">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D70" s="2">
         <v>26</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F70" s="2">
         <v>2</v>
       </c>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C70" t="s">
-        <v>35</v>
-      </c>
-      <c r="D70">
-        <v>30</v>
-      </c>
-      <c r="E70" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70">
-        <v>8</v>
-      </c>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
+        <v>35</v>
+      </c>
+      <c r="D71">
+        <v>30</v>
+      </c>
+      <c r="E71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C72" t="s">
         <v>41</v>
       </c>
-      <c r="D71">
+      <c r="D72">
         <v>35</v>
       </c>
-      <c r="E71" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71">
-        <v>8</v>
-      </c>
-      <c r="H71">
+      <c r="E72" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72">
+        <v>8</v>
+      </c>
+      <c r="H72">
         <v>60</v>
       </c>
-      <c r="I71" t="s">
-        <v>1</v>
-      </c>
-      <c r="J71">
+      <c r="I72" t="s">
+        <v>1</v>
+      </c>
+      <c r="J72">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B72" s="3" t="s">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B73" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D73" s="3">
         <v>44</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F73" s="3">
         <v>2</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G73" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C73" t="s">
-        <v>67</v>
-      </c>
-      <c r="D73">
-        <v>59</v>
-      </c>
-      <c r="E73" t="s">
-        <v>1</v>
-      </c>
-      <c r="F73">
-        <v>7</v>
-      </c>
+      <c r="H73" s="3"/>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C74" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="D74">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E74" t="s">
         <v>1</v>
       </c>
       <c r="F74">
-        <v>6</v>
-      </c>
-      <c r="G74" t="s">
-        <v>125</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C75" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D75">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E75" t="s">
         <v>1</v>
       </c>
       <c r="F75">
-        <v>9</v>
-      </c>
-      <c r="H75">
-        <v>62</v>
-      </c>
-      <c r="I75" t="s">
-        <v>1</v>
-      </c>
-      <c r="J75">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="G75" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
+        <v>126</v>
+      </c>
+      <c r="D76">
+        <v>71</v>
+      </c>
+      <c r="E76" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>9</v>
+      </c>
+      <c r="H76">
+        <v>62</v>
+      </c>
+      <c r="I76" t="s">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C77" t="s">
         <v>130</v>
       </c>
-      <c r="D76">
+      <c r="D77">
         <v>72</v>
       </c>
-      <c r="E76" t="s">
-        <v>1</v>
-      </c>
-      <c r="F76">
-        <v>9</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="E77" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>9</v>
+      </c>
+      <c r="G77" t="s">
         <v>131</v>
       </c>
-      <c r="H76">
+      <c r="H77">
         <v>64</v>
       </c>
-      <c r="I76" t="s">
-        <v>1</v>
-      </c>
-      <c r="J76">
-        <v>8</v>
-      </c>
-      <c r="K76" t="s">
+      <c r="I77" t="s">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>8</v>
+      </c>
+      <c r="K77" t="s">
         <v>131</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B3:S3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:O75">
-    <sortCondition ref="L4:L75"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:S77">
+    <sortCondition ref="P4:P77"/>
   </sortState>
   <mergeCells count="5">
     <mergeCell ref="B2:C2"/>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE9F83C-8698-44D7-A34F-6E4287488477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA1CBAE-A550-4AD6-987D-15C5E8191655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="142">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -297,9 +297,6 @@
     <t>Costilla, Marita</t>
   </si>
   <si>
-    <t>NO PRESENTO</t>
-  </si>
-  <si>
     <t>Balconte, Aldo Exequiel</t>
   </si>
   <si>
@@ -442,6 +439,21 @@
   </si>
   <si>
     <t>Flores, Ana Paula</t>
+  </si>
+  <si>
+    <t>Santillán, Ivan</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>Copia del 40</t>
+  </si>
+  <si>
+    <t>Copia del 39</t>
+  </si>
+  <si>
+    <t>Entrega Fuera de Término</t>
   </si>
 </sst>
 </file>
@@ -841,27 +853,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:S77"/>
+  <dimension ref="B2:S78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="54.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="54.28515625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="50.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="66.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="66.7109375" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="11" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="19.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.25">
@@ -870,25 +882,25 @@
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
       <c r="H2" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I2" s="10"/>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
       <c r="L2" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
       <c r="P2" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q2" s="10"/>
       <c r="R2" s="10"/>
@@ -902,60 +914,60 @@
         <v>15</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="L3" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="M3" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="N3" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>107</v>
-      </c>
       <c r="P3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q3" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="R3" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="S3" s="9" t="s">
         <v>135</v>
-      </c>
-      <c r="S3" s="9" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>1</v>
@@ -982,7 +994,7 @@
         <v>9</v>
       </c>
       <c r="O4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P4">
         <v>1</v>
@@ -996,16 +1008,16 @@
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5">
         <v>13</v>
@@ -1029,7 +1041,7 @@
         <v>9</v>
       </c>
       <c r="O5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P5">
         <v>2</v>
@@ -1043,10 +1055,10 @@
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
         <v>1</v>
@@ -1073,7 +1085,7 @@
         <v>9</v>
       </c>
       <c r="O6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P6">
         <v>3</v>
@@ -1086,16 +1098,22 @@
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7">
-        <v>51</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7">
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="H7">
@@ -1117,7 +1135,7 @@
         <v>9</v>
       </c>
       <c r="O7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P7">
         <v>4</v>
@@ -1127,17 +1145,23 @@
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8">
-        <v>49</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>8</v>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="H8">
         <v>17</v>
@@ -1158,7 +1182,7 @@
         <v>10</v>
       </c>
       <c r="O8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P8">
         <v>5</v>
@@ -1172,10 +1196,10 @@
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="D9">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E9" t="s">
         <v>1</v>
@@ -1202,7 +1226,7 @@
         <v>9</v>
       </c>
       <c r="O9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -1212,18 +1236,20 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C10" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10">
-        <v>56</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>9</v>
-      </c>
+      <c r="B10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6">
+        <v>7</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
       <c r="H10">
         <v>3</v>
       </c>
@@ -1243,7 +1269,7 @@
         <v>9</v>
       </c>
       <c r="O10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P10">
         <v>7</v>
@@ -1256,11 +1282,14 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" t="s">
         <v>1</v>
@@ -1287,7 +1316,7 @@
         <v>9</v>
       </c>
       <c r="O11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P11">
         <v>8</v>
@@ -1301,10 +1330,10 @@
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="E12" t="s">
         <v>1</v>
@@ -1331,7 +1360,7 @@
         <v>10</v>
       </c>
       <c r="O12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P12">
         <v>10</v>
@@ -1345,10 +1374,10 @@
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="D13">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>1</v>
@@ -1378,7 +1407,7 @@
         <v>5</v>
       </c>
       <c r="O13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P13">
         <v>11</v>
@@ -1390,15 +1419,15 @@
         <v>4</v>
       </c>
       <c r="S13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="D14">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
         <v>1</v>
@@ -1425,7 +1454,7 @@
         <v>8</v>
       </c>
       <c r="O14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P14">
         <v>12</v>
@@ -1438,21 +1467,23 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
-      <c r="C15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="B15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>12</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>2</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>37</v>
+      <c r="G15" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="H15" s="3">
         <v>1</v>
@@ -1476,7 +1507,7 @@
         <v>9</v>
       </c>
       <c r="O15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P15">
         <v>13</v>
@@ -1489,17 +1520,23 @@
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
-        <v>38</v>
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D16">
-        <v>32</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="H16">
         <v>28</v>
@@ -1520,7 +1557,7 @@
         <v>9</v>
       </c>
       <c r="O16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P16">
         <v>14</v>
@@ -1532,12 +1569,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C17" s="5" t="s">
-        <v>62</v>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>19</v>
       </c>
       <c r="D17">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
         <v>1</v>
@@ -1564,7 +1601,7 @@
         <v>8</v>
       </c>
       <c r="O17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P17">
         <v>15</v>
@@ -1576,18 +1613,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
-        <v>122</v>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="D18">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H18">
         <v>61</v>
@@ -1617,12 +1657,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>55</v>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="D19">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
         <v>1</v>
@@ -1649,7 +1692,7 @@
         <v>9</v>
       </c>
       <c r="O19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P19">
         <v>17</v>
@@ -1661,12 +1704,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D20">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
         <v>1</v>
@@ -1702,9 +1745,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>137</v>
+        <v>23</v>
+      </c>
+      <c r="D21">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>8</v>
       </c>
       <c r="P21">
         <v>19</v>
@@ -1716,18 +1768,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D22">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H22">
         <v>15</v>
@@ -1760,15 +1812,15 @@
         <v>10</v>
       </c>
       <c r="S22" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C23" s="5" t="s">
-        <v>54</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>25</v>
       </c>
       <c r="D23">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="E23" t="s">
         <v>1</v>
@@ -1777,16 +1829,16 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" t="s">
         <v>1</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="M23" t="s">
         <v>1</v>
@@ -1795,15 +1847,24 @@
         <v>9</v>
       </c>
       <c r="O23" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
-        <v>49</v>
+        <v>113</v>
+      </c>
+      <c r="P23">
+        <v>21</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C24" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="D24">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="E24" t="s">
         <v>1</v>
@@ -1830,7 +1891,7 @@
         <v>5</v>
       </c>
       <c r="O24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P24">
         <v>22</v>
@@ -1842,12 +1903,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
-        <v>40</v>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C25" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="D25">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
         <v>1</v>
@@ -1856,33 +1917,45 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I25" t="s">
         <v>1</v>
       </c>
       <c r="J25">
+        <v>7</v>
+      </c>
+      <c r="K25" t="s">
+        <v>78</v>
+      </c>
+      <c r="L25">
+        <v>33</v>
+      </c>
+      <c r="M25" t="s">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>6</v>
+      </c>
+      <c r="O25" t="s">
+        <v>120</v>
+      </c>
+      <c r="P25">
+        <v>23</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R25">
         <v>10</v>
       </c>
-      <c r="L25">
-        <v>10</v>
-      </c>
-      <c r="M25" t="s">
-        <v>1</v>
-      </c>
-      <c r="N25">
-        <v>7</v>
-      </c>
-      <c r="O25" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D26">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E26" t="s">
         <v>1</v>
@@ -1891,16 +1964,16 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I26" t="s">
         <v>1</v>
       </c>
       <c r="J26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M26" t="s">
         <v>1</v>
@@ -1909,15 +1982,24 @@
         <v>7</v>
       </c>
       <c r="O26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="P26">
+        <v>24</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
         <v>1</v>
@@ -1926,7 +2008,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I27" t="s">
         <v>1</v>
@@ -1934,108 +2016,115 @@
       <c r="J27">
         <v>7</v>
       </c>
-      <c r="K27" t="s">
-        <v>81</v>
-      </c>
       <c r="L27">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M27" t="s">
         <v>1</v>
       </c>
       <c r="N27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O27" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="P27">
+        <v>25</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D28">
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>8</v>
+      </c>
+      <c r="H28">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>7</v>
+      </c>
+      <c r="L28">
         <v>18</v>
       </c>
-      <c r="E28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <v>8</v>
-      </c>
-      <c r="H28">
-        <v>36</v>
-      </c>
-      <c r="I28" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28">
-        <v>9</v>
-      </c>
-      <c r="L28">
-        <v>17</v>
-      </c>
       <c r="M28" t="s">
         <v>1</v>
       </c>
       <c r="N28">
+        <v>9</v>
+      </c>
+      <c r="O28" t="s">
+        <v>113</v>
+      </c>
+      <c r="P28">
+        <v>26</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>1</v>
+      </c>
+      <c r="R28">
         <v>7</v>
       </c>
-      <c r="O28" t="s">
-        <v>117</v>
-      </c>
-      <c r="P28">
-        <v>24</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>1</v>
-      </c>
-      <c r="R28">
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
+      <c r="D29" s="2">
+        <v>26</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="2">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29">
+        <v>63</v>
+      </c>
+      <c r="I29" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>8</v>
+      </c>
+      <c r="P29">
+        <v>27</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>1</v>
+      </c>
+      <c r="R29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
         <v>32</v>
       </c>
-      <c r="D29">
+      <c r="D30">
         <v>27</v>
       </c>
-      <c r="E29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>8</v>
-      </c>
-      <c r="H29">
-        <v>16</v>
-      </c>
-      <c r="I29" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29">
-        <v>7</v>
-      </c>
-      <c r="L29">
-        <v>18</v>
-      </c>
-      <c r="M29" t="s">
-        <v>1</v>
-      </c>
-      <c r="N29">
-        <v>9</v>
-      </c>
-      <c r="O29" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30">
-        <v>36</v>
-      </c>
       <c r="E30" t="s">
         <v>1</v>
       </c>
@@ -2043,28 +2132,25 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="I30" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>9</v>
-      </c>
-      <c r="L30">
-        <v>22</v>
-      </c>
-      <c r="M30" t="s">
-        <v>1</v>
-      </c>
-      <c r="N30">
-        <v>9</v>
-      </c>
-      <c r="O30" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="P30">
+        <v>28</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>1</v>
+      </c>
+      <c r="R30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C31" s="5" t="s">
         <v>33</v>
       </c>
@@ -2078,28 +2164,28 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I31" t="s">
         <v>1</v>
       </c>
       <c r="J31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="M31" t="s">
         <v>1</v>
       </c>
       <c r="N31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O31" t="s">
         <v>114</v>
       </c>
       <c r="P31">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Q31" t="s">
         <v>1</v>
@@ -2108,12 +2194,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C32" s="5" t="s">
-        <v>26</v>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>34</v>
       </c>
       <c r="D32">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
         <v>1</v>
@@ -2122,7 +2208,7 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="I32" t="s">
         <v>1</v>
@@ -2130,136 +2216,170 @@
       <c r="J32">
         <v>6</v>
       </c>
+      <c r="K32" t="s">
+        <v>86</v>
+      </c>
       <c r="L32">
+        <v>35</v>
+      </c>
+      <c r="M32" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="O32" t="s">
+        <v>122</v>
+      </c>
+      <c r="P32">
+        <v>30</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>1</v>
+      </c>
+      <c r="R32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33">
+        <v>30</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+      <c r="H33">
+        <v>41</v>
+      </c>
+      <c r="I33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>8</v>
+      </c>
+      <c r="P33">
+        <v>31</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>1</v>
+      </c>
+      <c r="R33">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B34" s="3"/>
+      <c r="C34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="3">
+        <v>31</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="3">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H34">
+        <v>9</v>
+      </c>
+      <c r="I34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>6</v>
+      </c>
+      <c r="L34">
         <v>24</v>
       </c>
-      <c r="M32" t="s">
-        <v>1</v>
-      </c>
-      <c r="N32">
-        <v>8</v>
-      </c>
-      <c r="O32" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C33" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33">
+      <c r="M34" t="s">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>8</v>
+      </c>
+      <c r="O34" t="s">
+        <v>117</v>
+      </c>
+      <c r="P34">
+        <v>32</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>1</v>
+      </c>
+      <c r="R34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35">
+        <v>32</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>8</v>
+      </c>
+      <c r="H35">
+        <v>26</v>
+      </c>
+      <c r="I35" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>8</v>
+      </c>
+      <c r="L35">
+        <v>26</v>
+      </c>
+      <c r="M35" t="s">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>9</v>
+      </c>
+      <c r="O35" t="s">
+        <v>111</v>
+      </c>
+      <c r="P35">
+        <v>33</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>1</v>
+      </c>
+      <c r="R35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
         <v>39</v>
       </c>
-      <c r="E33" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33">
-        <v>8</v>
-      </c>
-      <c r="H33">
-        <v>26</v>
-      </c>
-      <c r="I33" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33">
-        <v>8</v>
-      </c>
-      <c r="L33">
-        <v>26</v>
-      </c>
-      <c r="M33" t="s">
-        <v>1</v>
-      </c>
-      <c r="N33">
-        <v>9</v>
-      </c>
-      <c r="O33" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C34" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34">
-        <v>40</v>
-      </c>
-      <c r="E34" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34">
-        <v>8</v>
-      </c>
-      <c r="H34">
-        <v>34</v>
-      </c>
-      <c r="I34" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34">
-        <v>9</v>
-      </c>
-      <c r="L34">
-        <v>27</v>
-      </c>
-      <c r="M34" t="s">
-        <v>1</v>
-      </c>
-      <c r="N34">
-        <v>8</v>
-      </c>
-      <c r="O34" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C35" t="s">
-        <v>92</v>
-      </c>
-      <c r="D35">
-        <v>67</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35">
-        <v>9</v>
-      </c>
-      <c r="H35">
+      <c r="D36">
+        <v>33</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>8</v>
+      </c>
+      <c r="H36">
         <v>57</v>
-      </c>
-      <c r="I35" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35">
-        <v>7</v>
-      </c>
-      <c r="L35">
-        <v>28</v>
-      </c>
-      <c r="M35" t="s">
-        <v>1</v>
-      </c>
-      <c r="N35">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C36" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36">
-        <v>3</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36">
-        <v>8</v>
-      </c>
-      <c r="H36">
-        <v>47</v>
       </c>
       <c r="I36" t="s">
         <v>1</v>
@@ -2268,7 +2388,7 @@
         <v>7</v>
       </c>
       <c r="L36">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M36" t="s">
         <v>1</v>
@@ -2276,13 +2396,22 @@
       <c r="N36">
         <v>9</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="P36">
+        <v>34</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>1</v>
+      </c>
+      <c r="R36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E37" t="s">
         <v>1</v>
@@ -2291,7 +2420,7 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I37" t="s">
         <v>1</v>
@@ -2299,25 +2428,22 @@
       <c r="J37">
         <v>8</v>
       </c>
-      <c r="L37">
-        <v>30</v>
-      </c>
-      <c r="M37" t="s">
-        <v>1</v>
-      </c>
-      <c r="N37">
-        <v>9</v>
-      </c>
-      <c r="O37" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="P37">
+        <v>35</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>1</v>
+      </c>
+      <c r="R37">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D38">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="E38" t="s">
         <v>1</v>
@@ -2326,7 +2452,7 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I38" t="s">
         <v>1</v>
@@ -2335,7 +2461,7 @@
         <v>9</v>
       </c>
       <c r="L38">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M38" t="s">
         <v>1</v>
@@ -2344,15 +2470,24 @@
         <v>9</v>
       </c>
       <c r="O38" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="P38">
+        <v>36</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>1</v>
+      </c>
+      <c r="R38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D39">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E39" t="s">
         <v>1</v>
@@ -2361,7 +2496,7 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I39" t="s">
         <v>1</v>
@@ -2369,627 +2504,693 @@
       <c r="J39">
         <v>7</v>
       </c>
-      <c r="K39" t="s">
-        <v>78</v>
-      </c>
       <c r="L39">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="M39" t="s">
         <v>1</v>
       </c>
       <c r="N39">
+        <v>9</v>
+      </c>
+      <c r="O39" t="s">
+        <v>108</v>
+      </c>
+      <c r="P39">
+        <v>41</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>1</v>
+      </c>
+      <c r="R39">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40">
+        <v>37</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>8</v>
+      </c>
+      <c r="H40">
+        <v>14</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <v>7</v>
+      </c>
+      <c r="K40" t="s">
+        <v>81</v>
+      </c>
+      <c r="L40">
+        <v>15</v>
+      </c>
+      <c r="M40" t="s">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>8</v>
+      </c>
+      <c r="O40" t="s">
+        <v>115</v>
+      </c>
+      <c r="P40">
+        <v>37</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>1</v>
+      </c>
+      <c r="R40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41">
+        <v>38</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>8</v>
+      </c>
+      <c r="H41">
+        <v>34</v>
+      </c>
+      <c r="I41" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>9</v>
+      </c>
+      <c r="L41">
+        <v>27</v>
+      </c>
+      <c r="M41" t="s">
+        <v>1</v>
+      </c>
+      <c r="N41">
+        <v>8</v>
+      </c>
+      <c r="O41" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42">
+        <v>39</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="H42">
+        <v>47</v>
+      </c>
+      <c r="I42" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>7</v>
+      </c>
+      <c r="L42">
+        <v>29</v>
+      </c>
+      <c r="M42" t="s">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>9</v>
+      </c>
+      <c r="P42">
+        <v>39</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>5</v>
+      </c>
+      <c r="R42">
+        <v>2</v>
+      </c>
+      <c r="S42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43">
+        <v>40</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+      <c r="H43">
+        <v>48</v>
+      </c>
+      <c r="I43" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>8</v>
+      </c>
+      <c r="L43">
+        <v>30</v>
+      </c>
+      <c r="M43" t="s">
+        <v>1</v>
+      </c>
+      <c r="N43">
+        <v>9</v>
+      </c>
+      <c r="O43" t="s">
+        <v>119</v>
+      </c>
+      <c r="P43">
+        <v>40</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>5</v>
+      </c>
+      <c r="R43">
+        <v>2</v>
+      </c>
+      <c r="S43" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44">
+        <v>41</v>
+      </c>
+      <c r="E44" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>8</v>
+      </c>
+      <c r="H44">
+        <v>49</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>9</v>
+      </c>
+      <c r="L44">
+        <v>32</v>
+      </c>
+      <c r="M44" t="s">
+        <v>1</v>
+      </c>
+      <c r="N44">
+        <v>9</v>
+      </c>
+      <c r="O44" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45">
+        <v>42</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>8</v>
+      </c>
+      <c r="H45">
         <v>6</v>
       </c>
-      <c r="O39" t="s">
-        <v>121</v>
-      </c>
-      <c r="P39">
-        <v>23</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>1</v>
-      </c>
-      <c r="R39">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C40" t="s">
-        <v>25</v>
-      </c>
-      <c r="D40">
-        <v>20</v>
-      </c>
-      <c r="E40" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40">
-        <v>8</v>
-      </c>
-      <c r="H40">
-        <v>33</v>
-      </c>
-      <c r="I40" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40">
+      <c r="I45" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45">
         <v>6</v>
       </c>
-      <c r="K40" t="s">
-        <v>86</v>
-      </c>
-      <c r="L40">
-        <v>35</v>
-      </c>
-      <c r="M40" t="s">
+      <c r="K45" t="s">
+        <v>74</v>
+      </c>
+      <c r="L45">
+        <v>36</v>
+      </c>
+      <c r="M45" t="s">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>7</v>
+      </c>
+      <c r="O45" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46">
+        <v>43</v>
+      </c>
+      <c r="E46" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>8</v>
+      </c>
+      <c r="H46">
+        <v>7</v>
+      </c>
+      <c r="I46" t="s">
         <v>5</v>
       </c>
-      <c r="N40">
-        <v>1</v>
-      </c>
-      <c r="O40" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C41" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41">
-        <v>22</v>
-      </c>
-      <c r="E41" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41">
-        <v>8</v>
-      </c>
-      <c r="H41">
-        <v>6</v>
-      </c>
-      <c r="I41" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41">
-        <v>6</v>
-      </c>
-      <c r="K41" t="s">
-        <v>74</v>
-      </c>
-      <c r="L41">
-        <v>36</v>
-      </c>
-      <c r="M41" t="s">
-        <v>1</v>
-      </c>
-      <c r="N41">
-        <v>7</v>
-      </c>
-      <c r="O41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D42">
-        <v>16</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42">
-        <v>8</v>
-      </c>
-      <c r="H42">
-        <v>7</v>
-      </c>
-      <c r="I42" t="s">
+      <c r="J46">
+        <v>2</v>
+      </c>
+      <c r="K46" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B47" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47" s="3">
+        <v>44</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J42">
+      <c r="F47" s="3">
         <v>2</v>
       </c>
-      <c r="K42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
-        <v>77</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43">
-        <v>15</v>
-      </c>
-      <c r="E43" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43">
-        <v>8</v>
-      </c>
-      <c r="H43">
-        <v>8</v>
-      </c>
-      <c r="I43" t="s">
-        <v>5</v>
-      </c>
-      <c r="J43">
-        <v>2</v>
-      </c>
-      <c r="K43" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44">
-        <v>8</v>
-      </c>
-      <c r="E44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>8</v>
-      </c>
-      <c r="H44">
-        <v>12</v>
-      </c>
-      <c r="I44" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44">
-        <v>2</v>
-      </c>
-      <c r="K44" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C45" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45">
-        <v>41</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45">
-        <v>8</v>
-      </c>
-      <c r="H45">
-        <v>19</v>
-      </c>
-      <c r="I45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C46" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46">
-        <v>57</v>
-      </c>
-      <c r="E46" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46">
-        <v>7</v>
-      </c>
-      <c r="H46">
-        <v>21</v>
-      </c>
-      <c r="I46" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46">
-        <v>8</v>
-      </c>
-      <c r="K46" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47">
-        <v>12</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="2">
-        <v>2</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H47" s="2">
-        <v>24</v>
-      </c>
-      <c r="I47" s="2" t="s">
+      <c r="G47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H47">
+        <v>8</v>
+      </c>
+      <c r="I47" t="s">
         <v>5</v>
       </c>
       <c r="J47">
         <v>2</v>
       </c>
       <c r="K47" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B48" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>17</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
+        <v>53</v>
       </c>
       <c r="D48">
-        <v>13</v>
-      </c>
-      <c r="E48" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>10</v>
+      </c>
+      <c r="H48">
+        <v>12</v>
+      </c>
+      <c r="I48" t="s">
         <v>5</v>
-      </c>
-      <c r="F48" s="2">
-        <v>2</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H48" s="2">
-        <v>29</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="J48">
         <v>2</v>
       </c>
       <c r="K48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C49" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49">
+        <v>46</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>8</v>
+      </c>
+      <c r="H49">
+        <v>19</v>
+      </c>
+      <c r="I49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50">
+        <v>47</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>8</v>
+      </c>
+      <c r="H50">
+        <v>21</v>
+      </c>
+      <c r="I50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>8</v>
+      </c>
+      <c r="K50" t="s">
+        <v>78</v>
+      </c>
+      <c r="P50">
+        <v>42</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>1</v>
+      </c>
+      <c r="R50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51">
+        <v>48</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+      <c r="H51" s="2">
+        <v>24</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J51">
+        <v>2</v>
+      </c>
+      <c r="K51" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52">
+        <v>49</v>
+      </c>
+      <c r="E52" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>8</v>
+      </c>
+      <c r="H52" s="2">
+        <v>29</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C49" t="s">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>58</v>
+      </c>
+      <c r="D53">
+        <v>50</v>
+      </c>
+      <c r="E53" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>8</v>
+      </c>
+      <c r="H53">
+        <v>30</v>
+      </c>
+      <c r="I53" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C54" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54">
+        <v>51</v>
+      </c>
+      <c r="E54" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>7</v>
+      </c>
+      <c r="H54">
+        <v>35</v>
+      </c>
+      <c r="I54" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55">
+        <v>52</v>
+      </c>
+      <c r="E55" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>9</v>
+      </c>
+      <c r="H55">
+        <v>42</v>
+      </c>
+      <c r="I55" t="s">
+        <v>1</v>
+      </c>
+      <c r="J55">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C56" t="s">
         <v>61</v>
       </c>
-      <c r="D49">
+      <c r="D56">
         <v>53</v>
       </c>
-      <c r="E49" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49">
-        <v>8</v>
-      </c>
-      <c r="H49">
-        <v>30</v>
-      </c>
-      <c r="I49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J49">
+      <c r="E56" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>8</v>
+      </c>
+      <c r="H56" s="2">
+        <v>44</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C57" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57">
+        <v>54</v>
+      </c>
+      <c r="E57" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>8</v>
+      </c>
+      <c r="H57">
+        <v>46</v>
+      </c>
+      <c r="I57" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C50" t="s">
-        <v>34</v>
-      </c>
-      <c r="D50">
-        <v>29</v>
-      </c>
-      <c r="E50" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50">
-        <v>8</v>
-      </c>
-      <c r="H50">
-        <v>35</v>
-      </c>
-      <c r="I50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C51" t="s">
-        <v>71</v>
-      </c>
-      <c r="D51">
+      <c r="J57">
+        <v>2</v>
+      </c>
+      <c r="K57" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C58" t="s">
         <v>63</v>
       </c>
-      <c r="E51" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51">
-        <v>8</v>
-      </c>
-      <c r="H51">
-        <v>41</v>
-      </c>
-      <c r="I51" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C52" t="s">
-        <v>30</v>
-      </c>
-      <c r="D52">
-        <v>25</v>
-      </c>
-      <c r="E52" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52">
-        <v>8</v>
-      </c>
-      <c r="H52">
-        <v>42</v>
-      </c>
-      <c r="I52" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C53" t="s">
-        <v>70</v>
-      </c>
-      <c r="D53">
-        <v>62</v>
-      </c>
-      <c r="E53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53">
-        <v>8</v>
-      </c>
-      <c r="H53">
-        <v>43</v>
-      </c>
-      <c r="I53" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" s="2">
-        <v>4</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" s="2">
-        <v>2</v>
-      </c>
-      <c r="G54" s="2" t="s">
+      <c r="D58">
+        <v>55</v>
+      </c>
+      <c r="E58" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>8</v>
+      </c>
+      <c r="H58">
+        <v>50</v>
+      </c>
+      <c r="I58" t="s">
+        <v>1</v>
+      </c>
+      <c r="L58">
+        <v>38</v>
+      </c>
+      <c r="M58" t="s">
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <v>10</v>
+      </c>
+      <c r="O58" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C59" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D59">
+        <v>56</v>
+      </c>
+      <c r="E59" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>9</v>
+      </c>
+      <c r="H59">
+        <v>51</v>
+      </c>
+      <c r="I59" t="s">
+        <v>1</v>
+      </c>
+      <c r="J59">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C60" t="s">
+        <v>65</v>
+      </c>
+      <c r="D60">
+        <v>57</v>
+      </c>
+      <c r="E60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60">
         <v>7</v>
       </c>
-      <c r="H54" s="2">
-        <v>44</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C55" t="s">
-        <v>68</v>
-      </c>
-      <c r="D55">
-        <v>60</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55">
-        <v>2</v>
-      </c>
-      <c r="H55">
-        <v>46</v>
-      </c>
-      <c r="I55" t="s">
-        <v>5</v>
-      </c>
-      <c r="J55">
-        <v>2</v>
-      </c>
-      <c r="K55" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C56" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56">
-        <v>17</v>
-      </c>
-      <c r="E56" t="s">
-        <v>1</v>
-      </c>
-      <c r="F56">
-        <v>8</v>
-      </c>
-      <c r="H56">
-        <v>50</v>
-      </c>
-      <c r="I56" t="s">
-        <v>1</v>
-      </c>
-      <c r="L56">
-        <v>38</v>
-      </c>
-      <c r="M56" t="s">
-        <v>1</v>
-      </c>
-      <c r="N56">
-        <v>10</v>
-      </c>
-      <c r="O56" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C57" t="s">
+      <c r="H60">
+        <v>52</v>
+      </c>
+      <c r="I60" t="s">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C61" t="s">
         <v>66</v>
       </c>
-      <c r="D57">
+      <c r="D61">
         <v>58</v>
       </c>
-      <c r="E57" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57">
-        <v>8</v>
-      </c>
-      <c r="H57">
-        <v>51</v>
-      </c>
-      <c r="I57" t="s">
-        <v>1</v>
-      </c>
-      <c r="J57">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C58" t="s">
-        <v>72</v>
-      </c>
-      <c r="D58">
-        <v>64</v>
-      </c>
-      <c r="E58" t="s">
-        <v>1</v>
-      </c>
-      <c r="F58">
-        <v>8</v>
-      </c>
-      <c r="H58">
-        <v>52</v>
-      </c>
-      <c r="I58" t="s">
-        <v>1</v>
-      </c>
-      <c r="J58">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C59" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59">
-        <v>6</v>
-      </c>
-      <c r="E59" t="s">
-        <v>1</v>
-      </c>
-      <c r="F59">
-        <v>8</v>
-      </c>
-      <c r="H59">
+      <c r="E61" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>8</v>
+      </c>
+      <c r="H61">
         <v>53</v>
       </c>
-      <c r="I59" t="s">
-        <v>1</v>
-      </c>
-      <c r="J59">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C60" t="s">
-        <v>88</v>
-      </c>
-      <c r="E60" t="s">
-        <v>89</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="H60">
-        <v>54</v>
-      </c>
-      <c r="I60" t="s">
-        <v>1</v>
-      </c>
-      <c r="J60">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C61" t="s">
-        <v>90</v>
-      </c>
-      <c r="D61">
-        <v>65</v>
-      </c>
-      <c r="E61" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61">
-        <v>8</v>
-      </c>
-      <c r="H61">
-        <v>55</v>
-      </c>
       <c r="I61" t="s">
         <v>1</v>
       </c>
       <c r="J61">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="D62">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E62" t="s">
         <v>1</v>
@@ -2998,7 +3199,7 @@
         <v>7</v>
       </c>
       <c r="H62">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I62" t="s">
         <v>1</v>
@@ -3007,30 +3208,30 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="D63">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E63" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F63">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H63">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I63" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J63">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
         <v>69</v>
       </c>
@@ -3044,148 +3245,139 @@
         <v>8</v>
       </c>
       <c r="H64">
+        <v>56</v>
+      </c>
+      <c r="I64" t="s">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C65" t="s">
+        <v>70</v>
+      </c>
+      <c r="D65">
+        <v>62</v>
+      </c>
+      <c r="E65" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>8</v>
+      </c>
+      <c r="H65">
         <v>59</v>
       </c>
-      <c r="I64" t="s">
-        <v>1</v>
-      </c>
-      <c r="J64">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C65" t="s">
-        <v>2</v>
-      </c>
-      <c r="D65">
-        <v>2</v>
-      </c>
-      <c r="E65" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" s="2" t="s">
+      <c r="I65" t="s">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C66" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66">
+        <v>63</v>
+      </c>
+      <c r="E66" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>72</v>
+      </c>
+      <c r="D67">
+        <v>64</v>
+      </c>
+      <c r="E67" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>8</v>
+      </c>
+      <c r="H67" s="2"/>
+    </row>
+    <row r="68" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C68" t="s">
+        <v>89</v>
+      </c>
+      <c r="D68">
+        <v>65</v>
+      </c>
+      <c r="E68" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C69" t="s">
+        <v>90</v>
+      </c>
+      <c r="D69">
+        <v>66</v>
+      </c>
+      <c r="E69" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C70" t="s">
+        <v>91</v>
+      </c>
+      <c r="D70">
+        <v>67</v>
+      </c>
+      <c r="E70" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>9</v>
+      </c>
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>92</v>
+      </c>
+      <c r="D71">
+        <v>68</v>
+      </c>
+      <c r="E71" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C72" t="s">
+        <v>123</v>
+      </c>
+      <c r="D72">
+        <v>69</v>
+      </c>
+      <c r="E72" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72">
         <v>6</v>
       </c>
-      <c r="D66" s="2">
-        <v>5</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" s="2">
-        <v>2</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H66" s="2"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B67" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D67" s="6">
-        <v>7</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C68" t="s">
-        <v>12</v>
-      </c>
-      <c r="D68">
-        <v>11</v>
-      </c>
-      <c r="E68" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C69" t="s">
-        <v>28</v>
-      </c>
-      <c r="D69">
-        <v>23</v>
-      </c>
-      <c r="E69" t="s">
-        <v>1</v>
-      </c>
-      <c r="F69">
-        <v>8</v>
-      </c>
-      <c r="H69">
-        <v>63</v>
-      </c>
-      <c r="I69" t="s">
-        <v>1</v>
-      </c>
-      <c r="J69">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D70" s="2">
-        <v>26</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F70" s="2">
-        <v>2</v>
-      </c>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C71" t="s">
-        <v>35</v>
-      </c>
-      <c r="D71">
-        <v>30</v>
-      </c>
-      <c r="E71" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C72" t="s">
-        <v>41</v>
-      </c>
-      <c r="D72">
-        <v>35</v>
-      </c>
-      <c r="E72" t="s">
-        <v>1</v>
-      </c>
-      <c r="F72">
-        <v>8</v>
+      <c r="G72" t="s">
+        <v>124</v>
       </c>
       <c r="H72">
         <v>60</v>
@@ -3197,70 +3389,67 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B73" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D73" s="3">
-        <v>44</v>
-      </c>
-      <c r="E73" s="3" t="s">
+    <row r="73" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>121</v>
+      </c>
+      <c r="D73">
+        <v>70</v>
+      </c>
+      <c r="E73" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73">
+        <v>9</v>
+      </c>
+      <c r="H73" s="3"/>
+    </row>
+    <row r="74" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C74" t="s">
+        <v>125</v>
+      </c>
+      <c r="D74">
+        <v>71</v>
+      </c>
+      <c r="E74" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C75" t="s">
+        <v>129</v>
+      </c>
+      <c r="D75">
+        <v>72</v>
+      </c>
+      <c r="E75" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75">
+        <v>9</v>
+      </c>
+      <c r="G75" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="76" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>136</v>
+      </c>
+      <c r="D76">
+        <v>73</v>
+      </c>
+      <c r="E76" t="s">
         <v>5</v>
       </c>
-      <c r="F73" s="3">
+      <c r="F76">
         <v>2</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C74" t="s">
-        <v>67</v>
-      </c>
-      <c r="D74">
-        <v>59</v>
-      </c>
-      <c r="E74" t="s">
-        <v>1</v>
-      </c>
-      <c r="F74">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C75" t="s">
-        <v>124</v>
-      </c>
-      <c r="D75">
-        <v>69</v>
-      </c>
-      <c r="E75" t="s">
-        <v>1</v>
-      </c>
-      <c r="F75">
-        <v>6</v>
-      </c>
-      <c r="G75" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C76" t="s">
-        <v>126</v>
-      </c>
-      <c r="D76">
-        <v>71</v>
-      </c>
-      <c r="E76" t="s">
-        <v>1</v>
-      </c>
-      <c r="F76">
-        <v>9</v>
+      <c r="G76" t="s">
+        <v>141</v>
       </c>
       <c r="H76">
         <v>62</v>
@@ -3272,21 +3461,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C77" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="D77">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E77" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F77">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G77" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="H77">
         <v>64</v>
@@ -3298,13 +3487,42 @@
         <v>8</v>
       </c>
       <c r="K77" t="s">
-        <v>131</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="78" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="C78" t="s">
+        <v>137</v>
+      </c>
+      <c r="D78">
+        <v>75</v>
+      </c>
+      <c r="E78" t="s">
+        <v>5</v>
+      </c>
+      <c r="F78">
+        <v>2</v>
+      </c>
+      <c r="G78" t="s">
+        <v>141</v>
+      </c>
+      <c r="P78">
+        <v>38</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>5</v>
+      </c>
+      <c r="R78">
+        <v>2</v>
+      </c>
+      <c r="S78" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B3:S3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:S77">
-    <sortCondition ref="P4:P77"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:G78">
+    <sortCondition ref="D4:D78"/>
   </sortState>
   <mergeCells count="5">
     <mergeCell ref="B2:C2"/>

--- a/00000_Correcciones/Cohoorte06.xlsx
+++ b/00000_Correcciones/Cohoorte06.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\00000_Correcciones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel M\Desktop\Modulo02_JavaScript\00000_Correcciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA1CBAE-A550-4AD6-987D-15C5E8191655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$3:$S$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="148">
   <si>
     <t>Acosta Nieva, Nicole Nazarena</t>
   </si>
@@ -454,12 +453,30 @@
   </si>
   <si>
     <t>Entrega Fuera de Término</t>
+  </si>
+  <si>
+    <t>ORDEN 5</t>
+  </si>
+  <si>
+    <t>RESULTADO 5</t>
+  </si>
+  <si>
+    <t>NOTA 5</t>
+  </si>
+  <si>
+    <t>OBSERVACIONES 5</t>
+  </si>
+  <si>
+    <t>TRABAJO PRÁCTICO NRO. 05</t>
+  </si>
+  <si>
+    <t>Entrego el TP 4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -559,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -570,6 +587,10 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -852,61 +873,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:S78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:X78"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="54.28515625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="54.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="50.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="66.7109375" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="11" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="9.85546875" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="19.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="66.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10" t="s">
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10" t="s">
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-    </row>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="10"/>
+    </row>
+    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
@@ -961,8 +992,20 @@
       <c r="S3" s="9" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T3" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>0</v>
       </c>
@@ -1006,7 +1049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>2</v>
       </c>
@@ -1053,7 +1096,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>3</v>
       </c>
@@ -1096,8 +1139,17 @@
       <c r="R6">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T6">
+        <v>9</v>
+      </c>
+      <c r="U6" t="s">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1144,7 +1196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
@@ -1194,7 +1246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>9</v>
       </c>
@@ -1235,7 +1287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
@@ -1281,7 +1333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>80</v>
       </c>
@@ -1328,7 +1380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>12</v>
       </c>
@@ -1372,7 +1424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>13</v>
       </c>
@@ -1421,8 +1473,20 @@
       <c r="S13" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13" t="s">
+        <v>5</v>
+      </c>
+      <c r="V13">
+        <v>2</v>
+      </c>
+      <c r="W13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>12</v>
       </c>
@@ -1466,7 +1530,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>31</v>
       </c>
@@ -1519,7 +1583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
@@ -1569,7 +1633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>19</v>
       </c>
@@ -1613,7 +1677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>77</v>
       </c>
@@ -1657,7 +1721,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>76</v>
       </c>
@@ -1704,7 +1768,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>22</v>
       </c>
@@ -1745,7 +1809,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>23</v>
       </c>
@@ -1768,7 +1832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>24</v>
       </c>
@@ -1814,8 +1878,17 @@
       <c r="S22" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T22">
+        <v>7</v>
+      </c>
+      <c r="U22" t="s">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>25</v>
       </c>
@@ -1859,7 +1932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C24" s="5" t="s">
         <v>26</v>
       </c>
@@ -1903,7 +1976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C25" s="5" t="s">
         <v>27</v>
       </c>
@@ -1950,7 +2023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>28</v>
       </c>
@@ -1994,7 +2067,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>29</v>
       </c>
@@ -2038,7 +2111,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>30</v>
       </c>
@@ -2082,7 +2155,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>8</v>
       </c>
@@ -2118,7 +2191,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>32</v>
       </c>
@@ -2150,7 +2223,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C31" s="5" t="s">
         <v>33</v>
       </c>
@@ -2194,7 +2267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>34</v>
       </c>
@@ -2241,7 +2314,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>35</v>
       </c>
@@ -2273,7 +2346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
       <c r="C34" s="5" t="s">
         <v>36</v>
@@ -2321,7 +2394,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>38</v>
       </c>
@@ -2364,8 +2437,17 @@
       <c r="R35">
         <v>6</v>
       </c>
-    </row>
-    <row r="36" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T35">
+        <v>5</v>
+      </c>
+      <c r="U35" t="s">
+        <v>1</v>
+      </c>
+      <c r="V35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>39</v>
       </c>
@@ -2406,7 +2488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
         <v>40</v>
       </c>
@@ -2438,7 +2520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>41</v>
       </c>
@@ -2482,7 +2564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>42</v>
       </c>
@@ -2526,7 +2608,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>43</v>
       </c>
@@ -2573,7 +2655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>44</v>
       </c>
@@ -2608,7 +2690,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>45</v>
       </c>
@@ -2652,7 +2734,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>46</v>
       </c>
@@ -2699,7 +2781,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>47</v>
       </c>
@@ -2734,7 +2816,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>48</v>
       </c>
@@ -2772,7 +2854,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>49</v>
       </c>
@@ -2798,7 +2880,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
         <v>51</v>
       </c>
@@ -2830,7 +2912,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>53</v>
       </c>
@@ -2856,7 +2938,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C49" s="5" t="s">
         <v>54</v>
       </c>
@@ -2878,8 +2960,17 @@
       <c r="J49">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="T49">
+        <v>6</v>
+      </c>
+      <c r="U49" t="s">
+        <v>1</v>
+      </c>
+      <c r="V49">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>55</v>
       </c>
@@ -2914,7 +3005,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
         <v>56</v>
       </c>
@@ -2939,8 +3030,17 @@
       <c r="K51" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="T51">
+        <v>4</v>
+      </c>
+      <c r="U51" t="s">
+        <v>1</v>
+      </c>
+      <c r="V51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C52" t="s">
         <v>57</v>
       </c>
@@ -2966,7 +3066,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C53" t="s">
         <v>58</v>
       </c>
@@ -2989,7 +3089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
         <v>59</v>
       </c>
@@ -3012,7 +3112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>60</v>
       </c>
@@ -3035,7 +3135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
         <v>61</v>
       </c>
@@ -3058,7 +3158,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C57" s="5" t="s">
         <v>62</v>
       </c>
@@ -3084,7 +3184,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
         <v>63</v>
       </c>
@@ -3116,7 +3216,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C59" s="5" t="s">
         <v>64</v>
       </c>
@@ -3139,7 +3239,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
         <v>65</v>
       </c>
@@ -3162,7 +3262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
         <v>66</v>
       </c>
@@ -3185,7 +3285,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
         <v>67</v>
       </c>
@@ -3208,7 +3308,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
         <v>68</v>
       </c>
@@ -3231,7 +3331,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
         <v>69</v>
       </c>
@@ -3254,7 +3354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C65" t="s">
         <v>70</v>
       </c>
@@ -3277,7 +3377,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C66" t="s">
         <v>71</v>
       </c>
@@ -3291,7 +3391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>72</v>
       </c>
@@ -3306,7 +3406,7 @@
       </c>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
         <v>89</v>
       </c>
@@ -3320,7 +3420,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C69" t="s">
         <v>90</v>
       </c>
@@ -3334,7 +3434,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>91</v>
       </c>
@@ -3348,8 +3448,17 @@
         <v>9</v>
       </c>
       <c r="H70" s="2"/>
-    </row>
-    <row r="71" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="T70">
+        <v>8</v>
+      </c>
+      <c r="U70" t="s">
+        <v>1</v>
+      </c>
+      <c r="V70">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
         <v>92</v>
       </c>
@@ -3362,8 +3471,17 @@
       <c r="F71">
         <v>9</v>
       </c>
-    </row>
-    <row r="72" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="T71">
+        <v>3</v>
+      </c>
+      <c r="U71" t="s">
+        <v>1</v>
+      </c>
+      <c r="V71">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C72" t="s">
         <v>123</v>
       </c>
@@ -3389,7 +3507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C73" t="s">
         <v>121</v>
       </c>
@@ -3404,7 +3522,7 @@
       </c>
       <c r="H73" s="3"/>
     </row>
-    <row r="74" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C74" t="s">
         <v>125</v>
       </c>
@@ -3418,7 +3536,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C75" t="s">
         <v>129</v>
       </c>
@@ -3435,7 +3553,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="76" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
         <v>136</v>
       </c>
@@ -3460,8 +3578,17 @@
       <c r="J76">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="T76">
+        <v>2</v>
+      </c>
+      <c r="U76" t="s">
+        <v>1</v>
+      </c>
+      <c r="V76">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C77" t="s">
         <v>88</v>
       </c>
@@ -3490,7 +3617,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="78" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
         <v>137</v>
       </c>
@@ -3520,11 +3647,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:S3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:G78">
+  <autoFilter ref="B3:S3"/>
+  <sortState ref="B4:G78">
     <sortCondition ref="D4:D78"/>
   </sortState>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="T2:W2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="H2:K2"/>
